--- a/database/event/7910/event_7910_evp_summary.xlsx
+++ b/database/event/7910/event_7910_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>4.3562</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4362</v>
+        <v>3.3604</v>
       </c>
       <c r="E2" t="n">
         <v>9.548999999999999</v>
@@ -548,7 +548,7 @@
         <v>1.8309</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2</v>
+        <v>1.1551</v>
       </c>
       <c r="E3" t="n">
         <v>4.0135</v>
@@ -594,7 +594,7 @@
         <v>1.7517</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1299</v>
+        <v>1.0859</v>
       </c>
       <c r="E4" t="n">
         <v>3.8399</v>
@@ -640,7 +640,7 @@
         <v>1.6691</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0567</v>
+        <v>1.0137</v>
       </c>
       <c r="E5" t="n">
         <v>3.6587</v>
@@ -686,7 +686,7 @@
         <v>1.6013</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9966</v>
+        <v>0.9545</v>
       </c>
       <c r="E6" t="n">
         <v>3.5101</v>
@@ -732,7 +732,7 @@
         <v>1.4277</v>
       </c>
       <c r="D7" t="n">
-        <v>0.843</v>
+        <v>0.803</v>
       </c>
       <c r="E7" t="n">
         <v>3.1297</v>
@@ -778,7 +778,7 @@
         <v>1.4196</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8358</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="E8" t="n">
         <v>3.1119</v>
@@ -824,7 +824,7 @@
         <v>1.0468</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5056</v>
+        <v>0.4703</v>
       </c>
       <c r="E9" t="n">
         <v>2.2946</v>
@@ -870,7 +870,7 @@
         <v>0.9627</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4311</v>
+        <v>0.3968</v>
       </c>
       <c r="E10" t="n">
         <v>2.1102</v>
@@ -916,7 +916,7 @@
         <v>0.8964</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3725</v>
+        <v>0.3389</v>
       </c>
       <c r="E11" t="n">
         <v>1.965</v>
@@ -962,7 +962,7 @@
         <v>0.833</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3163</v>
+        <v>0.2836</v>
       </c>
       <c r="E12" t="n">
         <v>1.8261</v>
@@ -1008,7 +1008,7 @@
         <v>0.7701</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2606</v>
+        <v>0.2287</v>
       </c>
       <c r="E13" t="n">
         <v>1.6882</v>
@@ -1054,7 +1054,7 @@
         <v>0.7338</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2285</v>
+        <v>0.197</v>
       </c>
       <c r="E14" t="n">
         <v>1.6086</v>
@@ -1100,7 +1100,7 @@
         <v>0.6997</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1982</v>
+        <v>0.1671</v>
       </c>
       <c r="E15" t="n">
         <v>1.5337</v>
@@ -1146,7 +1146,7 @@
         <v>0.5321</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0498</v>
+        <v>0.0208</v>
       </c>
       <c r="E16" t="n">
         <v>1.1664</v>
@@ -1192,7 +1192,7 @@
         <v>0.4921</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0144</v>
+        <v>-0.0142</v>
       </c>
       <c r="E17" t="n">
         <v>1.0787</v>
@@ -1238,7 +1238,7 @@
         <v>0.345</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1158</v>
+        <v>-0.1426</v>
       </c>
       <c r="E18" t="n">
         <v>0.7563</v>
@@ -1284,7 +1284,7 @@
         <v>0.2673</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1846</v>
+        <v>-0.2104</v>
       </c>
       <c r="E19" t="n">
         <v>0.586</v>
@@ -1330,7 +1330,7 @@
         <v>0.2335</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2146</v>
+        <v>-0.24</v>
       </c>
       <c r="E20" t="n">
         <v>0.5119</v>
@@ -1376,7 +1376,7 @@
         <v>0.1346</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3021</v>
+        <v>-0.3263</v>
       </c>
       <c r="E21" t="n">
         <v>0.2951</v>
@@ -1422,7 +1422,7 @@
         <v>0.08110000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3495</v>
+        <v>-0.3731</v>
       </c>
       <c r="E22" t="n">
         <v>0.1778</v>
@@ -1468,7 +1468,7 @@
         <v>0.0725</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3571</v>
+        <v>-0.3806</v>
       </c>
       <c r="E23" t="n">
         <v>0.159</v>
@@ -1514,7 +1514,7 @@
         <v>0.0271</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3973</v>
+        <v>-0.4202</v>
       </c>
       <c r="E24" t="n">
         <v>0.0595</v>
@@ -1560,7 +1560,7 @@
         <v>-0.0014</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4226</v>
+        <v>-0.4451</v>
       </c>
       <c r="E25" t="n">
         <v>-0.003</v>
@@ -1606,7 +1606,7 @@
         <v>-0.0785</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4908</v>
+        <v>-0.5124</v>
       </c>
       <c r="E26" t="n">
         <v>-0.172</v>
@@ -1652,7 +1652,7 @@
         <v>-0.08119999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4933</v>
+        <v>-0.5149</v>
       </c>
       <c r="E27" t="n">
         <v>-0.1781</v>
@@ -1698,7 +1698,7 @@
         <v>-0.0881</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4994</v>
+        <v>-0.5209</v>
       </c>
       <c r="E28" t="n">
         <v>-0.1932</v>
@@ -1744,7 +1744,7 @@
         <v>-0.1229</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5302</v>
+        <v>-0.5512</v>
       </c>
       <c r="E29" t="n">
         <v>-0.2694</v>
@@ -1790,7 +1790,7 @@
         <v>-0.3027</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6894</v>
+        <v>-0.7082000000000001</v>
       </c>
       <c r="E30" t="n">
         <v>-0.6635</v>
@@ -1836,7 +1836,7 @@
         <v>-0.3051</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6915</v>
+        <v>-0.7104</v>
       </c>
       <c r="E31" t="n">
         <v>-0.6688</v>
@@ -1882,7 +1882,7 @@
         <v>-0.357</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7375</v>
+        <v>-0.7557</v>
       </c>
       <c r="E32" t="n">
         <v>-0.7825</v>
@@ -1928,7 +1928,7 @@
         <v>-0.3731</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7517</v>
+        <v>-0.7697000000000001</v>
       </c>
       <c r="E33" t="n">
         <v>-0.8178</v>
@@ -1974,7 +1974,7 @@
         <v>-0.4353</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8068</v>
+        <v>-0.824</v>
       </c>
       <c r="E34" t="n">
         <v>-0.9540999999999999</v>
@@ -2020,7 +2020,7 @@
         <v>-0.476</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8429</v>
+        <v>-0.8596</v>
       </c>
       <c r="E35" t="n">
         <v>-1.0435</v>
@@ -2066,7 +2066,7 @@
         <v>-0.49</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8552999999999999</v>
+        <v>-0.8719</v>
       </c>
       <c r="E36" t="n">
         <v>-1.0742</v>
@@ -2112,7 +2112,7 @@
         <v>-0.593</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9465</v>
+        <v>-0.9618</v>
       </c>
       <c r="E37" t="n">
         <v>-1.3</v>
@@ -2158,7 +2158,7 @@
         <v>-0.593</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9465</v>
+        <v>-0.9618</v>
       </c>
       <c r="E38" t="n">
         <v>-1.3</v>
@@ -2204,7 +2204,7 @@
         <v>-0.593</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9465</v>
+        <v>-0.9618</v>
       </c>
       <c r="E39" t="n">
         <v>-1.3</v>
@@ -2250,7 +2250,7 @@
         <v>-0.593</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.9465</v>
+        <v>-0.9618</v>
       </c>
       <c r="E40" t="n">
         <v>-1.3</v>
@@ -2296,7 +2296,7 @@
         <v>-0.7824</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1142</v>
+        <v>-1.1272</v>
       </c>
       <c r="E41" t="n">
         <v>-1.715</v>

--- a/database/event/7910/event_7910_evp_summary.xlsx
+++ b/database/event/7910/event_7910_evp_summary.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.548999999999999</v>
+        <v>8.7639</v>
       </c>
       <c r="C2" t="n">
-        <v>4.3562</v>
+        <v>3.998</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3604</v>
+        <v>3.3184</v>
       </c>
       <c r="E2" t="n">
-        <v>9.548999999999999</v>
+        <v>8.7639</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>9.548999999999999</v>
+        <v>8.7639</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>7.3454</v>
+        <v>6.2807</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>158</v>
       </c>
       <c r="M2" t="n">
-        <v>7.3454</v>
+        <v>6.2807</v>
       </c>
       <c r="N2" t="n">
         <v>158</v>
@@ -538,26 +538,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.0135</v>
+        <v>3.7659</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8309</v>
+        <v>1.718</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1551</v>
+        <v>1.0621</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0135</v>
+        <v>3.7659</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>4.0135</v>
+        <v>3.7659</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -566,44 +566,44 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0873</v>
+        <v>2.6989</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>86</v>
+        <v>158</v>
       </c>
       <c r="M3" t="n">
-        <v>3.0873</v>
+        <v>2.6989</v>
       </c>
       <c r="N3" t="n">
-        <v>86</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.8399</v>
+        <v>3.4799</v>
       </c>
       <c r="C4" t="n">
-        <v>1.7517</v>
+        <v>1.5875</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0859</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8399</v>
+        <v>3.4799</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8399</v>
+        <v>3.4799</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -612,44 +612,44 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9538</v>
+        <v>2.4939</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>168</v>
+        <v>86</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9538</v>
+        <v>2.4939</v>
       </c>
       <c r="N4" t="n">
-        <v>168</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>zweih</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.6587</v>
+        <v>3.3171</v>
       </c>
       <c r="C5" t="n">
-        <v>1.6691</v>
+        <v>1.5132</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0137</v>
+        <v>0.8595</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6587</v>
+        <v>3.3171</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6587</v>
+        <v>3.3171</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8144</v>
+        <v>2.3773</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>158</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8144</v>
+        <v>2.3773</v>
       </c>
       <c r="N5" t="n">
         <v>158</v>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.5101</v>
+        <v>3.0134</v>
       </c>
       <c r="C6" t="n">
-        <v>1.6013</v>
+        <v>1.3747</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9545</v>
+        <v>0.7224</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5101</v>
+        <v>3.0134</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3.5101</v>
+        <v>3.0134</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7001</v>
+        <v>2.1596</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>158</v>
       </c>
       <c r="M6" t="n">
-        <v>2.7001</v>
+        <v>2.1596</v>
       </c>
       <c r="N6" t="n">
         <v>158</v>
@@ -722,26 +722,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>zweih</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.1297</v>
+        <v>2.8905</v>
       </c>
       <c r="C7" t="n">
-        <v>1.4277</v>
+        <v>1.3186</v>
       </c>
       <c r="D7" t="n">
-        <v>0.803</v>
+        <v>0.6669</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1297</v>
+        <v>2.8905</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1297</v>
+        <v>2.8905</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -750,19 +750,19 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4075</v>
+        <v>2.0715</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="M7" t="n">
-        <v>2.4075</v>
+        <v>2.0715</v>
       </c>
       <c r="N7" t="n">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.1119</v>
+        <v>2.8034</v>
       </c>
       <c r="C8" t="n">
-        <v>1.4196</v>
+        <v>1.2789</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.6276</v>
       </c>
       <c r="E8" t="n">
-        <v>3.1119</v>
+        <v>2.8034</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3.1119</v>
+        <v>2.8034</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.3938</v>
+        <v>2.0091</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>168</v>
       </c>
       <c r="M8" t="n">
-        <v>2.3938</v>
+        <v>2.0091</v>
       </c>
       <c r="N8" t="n">
         <v>168</v>
@@ -818,22 +818,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.2946</v>
+        <v>1.8502</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0468</v>
+        <v>0.844</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4703</v>
+        <v>0.1973</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2946</v>
+        <v>1.8502</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2946</v>
+        <v>1.8502</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7651</v>
+        <v>1.326</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>108</v>
       </c>
       <c r="M9" t="n">
-        <v>1.7651</v>
+        <v>1.326</v>
       </c>
       <c r="N9" t="n">
         <v>108</v>
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.1102</v>
+        <v>1.8249</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9627</v>
+        <v>0.8325</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3968</v>
+        <v>0.1858</v>
       </c>
       <c r="E10" t="n">
-        <v>2.1102</v>
+        <v>1.8249</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1102</v>
+        <v>1.8249</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6232</v>
+        <v>1.3078</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>86</v>
       </c>
       <c r="M10" t="n">
-        <v>1.6232</v>
+        <v>1.3078</v>
       </c>
       <c r="N10" t="n">
         <v>86</v>
@@ -910,22 +910,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.965</v>
+        <v>1.8091</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8964</v>
+        <v>0.8253</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3389</v>
+        <v>0.1787</v>
       </c>
       <c r="E11" t="n">
-        <v>1.965</v>
+        <v>1.8091</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.965</v>
+        <v>1.8091</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -934,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5115</v>
+        <v>1.2965</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>108</v>
       </c>
       <c r="M11" t="n">
-        <v>1.5115</v>
+        <v>1.2965</v>
       </c>
       <c r="N11" t="n">
         <v>108</v>
@@ -952,26 +952,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.8261</v>
+        <v>1.7506</v>
       </c>
       <c r="C12" t="n">
-        <v>0.833</v>
+        <v>0.7986</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2836</v>
+        <v>0.1523</v>
       </c>
       <c r="E12" t="n">
-        <v>1.8261</v>
+        <v>1.7506</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1.8261</v>
+        <v>1.7506</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -980,44 +980,44 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.4047</v>
+        <v>1.2546</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="M12" t="n">
-        <v>1.4047</v>
+        <v>1.2546</v>
       </c>
       <c r="N12" t="n">
-        <v>86</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.6882</v>
+        <v>1.5731</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7701</v>
+        <v>0.7176</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2287</v>
+        <v>0.0722</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6882</v>
+        <v>1.5731</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.6882</v>
+        <v>1.5731</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1026,44 +1026,44 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.2986</v>
+        <v>1.1274</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2986</v>
+        <v>1.1274</v>
       </c>
       <c r="N13" t="n">
-        <v>39</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>jottAAA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.6086</v>
+        <v>1.5562</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7338</v>
+        <v>0.7099</v>
       </c>
       <c r="D14" t="n">
-        <v>0.197</v>
+        <v>0.0645</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6086</v>
+        <v>1.5562</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.6086</v>
+        <v>1.5562</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1072,44 +1072,44 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2374</v>
+        <v>1.1153</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>168</v>
+        <v>53</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2374</v>
+        <v>1.1153</v>
       </c>
       <c r="N14" t="n">
-        <v>168</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>jottAAA</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.5337</v>
+        <v>1.4907</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6997</v>
+        <v>0.68</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1671</v>
+        <v>0.035</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5337</v>
+        <v>1.4907</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5337</v>
+        <v>1.4907</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1118,19 +1118,19 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1798</v>
+        <v>1.0683</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>53</v>
+        <v>168</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1798</v>
+        <v>1.0683</v>
       </c>
       <c r="N15" t="n">
-        <v>53</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16">
@@ -1140,22 +1140,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.1664</v>
+        <v>1.261</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5321</v>
+        <v>0.5753</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0208</v>
+        <v>-0.0687</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1664</v>
+        <v>1.261</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1664</v>
+        <v>1.261</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8972</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>53</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8972</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="N16" t="n">
         <v>53</v>
@@ -1186,22 +1186,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.0787</v>
+        <v>1.1907</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4921</v>
+        <v>0.5432</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0142</v>
+        <v>-0.1005</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0787</v>
+        <v>1.1907</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0787</v>
+        <v>1.1907</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8298</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>108</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8298</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="N17" t="n">
         <v>108</v>
@@ -1228,26 +1228,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7563</v>
+        <v>0.888</v>
       </c>
       <c r="C18" t="n">
-        <v>0.345</v>
+        <v>0.4051</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1426</v>
+        <v>-0.2371</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7563</v>
+        <v>0.888</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7563</v>
+        <v>0.888</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1256,44 +1256,44 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5818</v>
+        <v>0.6364</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>64</v>
+        <v>168</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5818</v>
+        <v>0.6364</v>
       </c>
       <c r="N18" t="n">
-        <v>64</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.586</v>
+        <v>0.7794</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2673</v>
+        <v>0.3556</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2104</v>
+        <v>-0.2862</v>
       </c>
       <c r="E19" t="n">
-        <v>0.586</v>
+        <v>0.7794</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.586</v>
+        <v>0.7794</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1302,19 +1302,19 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4508</v>
+        <v>0.5586</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>168</v>
+        <v>64</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4508</v>
+        <v>0.5586</v>
       </c>
       <c r="N19" t="n">
-        <v>168</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
@@ -1324,22 +1324,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5119</v>
+        <v>0.6454</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2335</v>
+        <v>0.2944</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.24</v>
+        <v>-0.3466</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5119</v>
+        <v>0.6454</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5119</v>
+        <v>0.6454</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3938</v>
+        <v>0.4625</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>39</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3938</v>
+        <v>0.4625</v>
       </c>
       <c r="N20" t="n">
         <v>39</v>
@@ -1370,22 +1370,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2951</v>
+        <v>0.3035</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1346</v>
+        <v>0.1385</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3263</v>
+        <v>-0.501</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2951</v>
+        <v>0.3035</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2951</v>
+        <v>0.3035</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.227</v>
+        <v>0.2175</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>64</v>
       </c>
       <c r="M21" t="n">
-        <v>0.227</v>
+        <v>0.2175</v>
       </c>
       <c r="N21" t="n">
         <v>64</v>
@@ -1412,26 +1412,26 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1778</v>
+        <v>0.2856</v>
       </c>
       <c r="C22" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.1303</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3731</v>
+        <v>-0.5091</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1778</v>
+        <v>0.2856</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1778</v>
+        <v>0.2856</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1440,44 +1440,44 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1368</v>
+        <v>0.2047</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>158</v>
+        <v>53</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1368</v>
+        <v>0.2047</v>
       </c>
       <c r="N22" t="n">
-        <v>158</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.159</v>
+        <v>0.2538</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0725</v>
+        <v>0.1158</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3806</v>
+        <v>-0.5234</v>
       </c>
       <c r="E23" t="n">
-        <v>0.159</v>
+        <v>0.2538</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.159</v>
+        <v>0.2538</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1486,44 +1486,44 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1223</v>
+        <v>0.1819</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>64</v>
+        <v>158</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1223</v>
+        <v>0.1819</v>
       </c>
       <c r="N23" t="n">
-        <v>64</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0595</v>
+        <v>0.2343</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0271</v>
+        <v>0.1069</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4202</v>
+        <v>-0.5322</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0595</v>
+        <v>0.2343</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0595</v>
+        <v>0.2343</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1532,44 +1532,44 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0458</v>
+        <v>0.1679</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0458</v>
+        <v>0.1679</v>
       </c>
       <c r="N24" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.003</v>
+        <v>0.059</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0014</v>
+        <v>0.0269</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4451</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.003</v>
+        <v>0.059</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.003</v>
+        <v>0.059</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1578,44 +1578,44 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.0023</v>
+        <v>0.0423</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>168</v>
+        <v>38</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0023</v>
+        <v>0.0423</v>
       </c>
       <c r="N25" t="n">
-        <v>168</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.172</v>
+        <v>0.0359</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0785</v>
+        <v>0.0164</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5124</v>
+        <v>-0.6218</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.172</v>
+        <v>0.0359</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.172</v>
+        <v>0.0359</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1624,44 +1624,44 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.1323</v>
+        <v>0.0257</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1323</v>
+        <v>0.0257</v>
       </c>
       <c r="N26" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1781</v>
+        <v>-0.0018</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.0008</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5149</v>
+        <v>-0.6388</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.1781</v>
+        <v>-0.0018</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.1781</v>
+        <v>-0.0018</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1670,7 +1670,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.137</v>
+        <v>-0.0013</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>38</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.137</v>
+        <v>-0.0013</v>
       </c>
       <c r="N27" t="n">
         <v>38</v>
@@ -1688,26 +1688,26 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1932</v>
+        <v>-0.0631</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0881</v>
+        <v>-0.0288</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5209</v>
+        <v>-0.6665</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1932</v>
+        <v>-0.0631</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.1932</v>
+        <v>-0.0631</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1716,44 +1716,44 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.1486</v>
+        <v>-0.0452</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1486</v>
+        <v>-0.0452</v>
       </c>
       <c r="N28" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2694</v>
+        <v>-0.1899</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1229</v>
+        <v>-0.0866</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5512</v>
+        <v>-0.7237</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2694</v>
+        <v>-0.1899</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.2694</v>
+        <v>-0.1899</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1762,19 +1762,19 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.2072</v>
+        <v>-0.1361</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>38</v>
+        <v>168</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2072</v>
+        <v>-0.1361</v>
       </c>
       <c r="N29" t="n">
-        <v>38</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30">
@@ -1784,22 +1784,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.6635</v>
+        <v>-0.3846</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3027</v>
+        <v>-0.1755</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7082000000000001</v>
+        <v>-0.8116</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.6635</v>
+        <v>-0.3846</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.6635</v>
+        <v>-0.3846</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1808,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.5104</v>
+        <v>-0.2756</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>64</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.5104</v>
+        <v>-0.2756</v>
       </c>
       <c r="N30" t="n">
         <v>64</v>
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.6688</v>
+        <v>-0.4483</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3051</v>
+        <v>-0.2045</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7104</v>
+        <v>-0.8404</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.6688</v>
+        <v>-0.4483</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.6688</v>
+        <v>-0.4483</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.5145</v>
+        <v>-0.3213</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>53</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.5145</v>
+        <v>-0.3213</v>
       </c>
       <c r="N31" t="n">
         <v>53</v>
@@ -1872,26 +1872,26 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.7825</v>
+        <v>-0.5413</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.357</v>
+        <v>-0.2469</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7557</v>
+        <v>-0.8824</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.7825</v>
+        <v>-0.5413</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.7825</v>
+        <v>-0.5413</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1900,44 +1900,44 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.6019</v>
+        <v>-0.3879</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.6019</v>
+        <v>-0.3879</v>
       </c>
       <c r="N32" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.8178</v>
+        <v>-0.6018</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3731</v>
+        <v>-0.2745</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7697000000000001</v>
+        <v>-0.9097</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.8178</v>
+        <v>-0.6018</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.8178</v>
+        <v>-0.6018</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1946,44 +1946,44 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.6291</v>
+        <v>-0.4313</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.6291</v>
+        <v>-0.4313</v>
       </c>
       <c r="N33" t="n">
-        <v>64</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9540999999999999</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4353</v>
+        <v>-0.3046</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.824</v>
+        <v>-0.9395</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9540999999999999</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.9540999999999999</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1992,44 +1992,44 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.7339</v>
+        <v>-0.4786</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7339</v>
+        <v>-0.4786</v>
       </c>
       <c r="N34" t="n">
-        <v>86</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.0435</v>
+        <v>-0.7059</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.476</v>
+        <v>-0.322</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8596</v>
+        <v>-0.9567</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.0435</v>
+        <v>-0.7059</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-1.0435</v>
+        <v>-0.7059</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2038,44 +2038,44 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.8027</v>
+        <v>-0.5059</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8027</v>
+        <v>-0.5059</v>
       </c>
       <c r="N35" t="n">
-        <v>108</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.0742</v>
+        <v>-0.8001</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.49</v>
+        <v>-0.365</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8719</v>
+        <v>-0.9992</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.0742</v>
+        <v>-0.8001</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.0742</v>
+        <v>-0.8001</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.8263</v>
+        <v>-0.5734</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>108</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8263</v>
+        <v>-0.5734</v>
       </c>
       <c r="N36" t="n">
         <v>108</v>
@@ -2102,26 +2102,26 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ICY</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.3</v>
+        <v>-0.9952</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.593</v>
+        <v>-0.454</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9618</v>
+        <v>-1.0873</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.3</v>
+        <v>-0.9952</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.3</v>
+        <v>-0.9952</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2130,44 +2130,44 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>-1</v>
+        <v>-0.7131999999999999</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M37" t="n">
-        <v>-1</v>
+        <v>-0.7131999999999999</v>
       </c>
       <c r="N37" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>ICY</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.3</v>
+        <v>-1.0728</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.593</v>
+        <v>-0.4894</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9618</v>
+        <v>-1.1223</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.3</v>
+        <v>-1.0728</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.3</v>
+        <v>-1.0728</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2176,44 +2176,44 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>-1</v>
+        <v>-0.7688</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M38" t="n">
-        <v>-1</v>
+        <v>-0.7688</v>
       </c>
       <c r="N38" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.3</v>
+        <v>-1.2562</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.593</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9618</v>
+        <v>-1.2051</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.3</v>
+        <v>-1.2562</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.3</v>
+        <v>-1.2562</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2222,44 +2222,44 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>-1</v>
+        <v>-0.9003</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="M39" t="n">
-        <v>-1</v>
+        <v>-0.9003</v>
       </c>
       <c r="N39" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3</v>
+        <v>-1.3114</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.593</v>
+        <v>-0.5982</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.9618</v>
+        <v>-1.23</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3</v>
+        <v>-1.3114</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.3</v>
+        <v>-1.3114</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2268,44 +2268,44 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>-1</v>
+        <v>-0.9398</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="M40" t="n">
-        <v>-1</v>
+        <v>-0.9398</v>
       </c>
       <c r="N40" t="n">
-        <v>39</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.715</v>
+        <v>-1.3273</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.7824</v>
+        <v>-0.6055</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1272</v>
+        <v>-1.2372</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.715</v>
+        <v>-1.3273</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.715</v>
+        <v>-1.3273</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2314,19 +2314,19 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.3192</v>
+        <v>-0.9512</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.3192</v>
+        <v>-0.9512</v>
       </c>
       <c r="N41" t="n">
-        <v>86</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -2429,10 +2429,10 @@
         <v>1.34</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9165</v>
+        <v>0.9052</v>
       </c>
       <c r="J2" t="n">
-        <v>21.996</v>
+        <v>21.7248</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5807</v>
+        <v>0.5718</v>
       </c>
       <c r="J3" t="n">
-        <v>13.9368</v>
+        <v>13.7232</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.13</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3649</v>
+        <v>0.3966</v>
       </c>
       <c r="J4" t="n">
-        <v>8.7576</v>
+        <v>9.5184</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.06</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1448</v>
+        <v>0.1987</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4752</v>
+        <v>4.7688</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.97</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2384</v>
+        <v>-0.1665</v>
       </c>
       <c r="J6" t="n">
-        <v>-5.7216</v>
+        <v>-3.996</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.13</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3154</v>
+        <v>0.3402</v>
       </c>
       <c r="J7" t="n">
-        <v>7.5696</v>
+        <v>8.1648</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1574</v>
+        <v>0.1424</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7776</v>
+        <v>3.4176</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.02</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1138</v>
+        <v>0.0902</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7312</v>
+        <v>2.1648</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.68</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-0.3429</v>
       </c>
       <c r="J10" t="n">
-        <v>-12.6168</v>
+        <v>-8.2296</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.62</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6038</v>
+        <v>-0.3992</v>
       </c>
       <c r="J11" t="n">
-        <v>-14.4912</v>
+        <v>-9.5808</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.42</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0796</v>
+        <v>1.0468</v>
       </c>
       <c r="J12" t="n">
-        <v>31.3084</v>
+        <v>30.3572</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.18</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5122</v>
+        <v>0.5185</v>
       </c>
       <c r="J13" t="n">
-        <v>14.8538</v>
+        <v>15.0365</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.1</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2592</v>
+        <v>0.3121</v>
       </c>
       <c r="J14" t="n">
-        <v>7.5168</v>
+        <v>9.0509</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.09</v>
       </c>
       <c r="I15" t="n">
-        <v>0.229</v>
+        <v>0.2838</v>
       </c>
       <c r="J15" t="n">
-        <v>6.641</v>
+        <v>8.2302</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1068</v>
+        <v>-0.0379</v>
       </c>
       <c r="J16" t="n">
-        <v>-3.0972</v>
+        <v>-1.0991</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.07</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1865</v>
+        <v>0.1908</v>
       </c>
       <c r="J17" t="n">
-        <v>5.4085</v>
+        <v>5.5332</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.06</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1678</v>
+        <v>0.1687</v>
       </c>
       <c r="J18" t="n">
-        <v>4.8662</v>
+        <v>4.8923</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.02</v>
       </c>
       <c r="I19" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.0716</v>
       </c>
       <c r="J19" t="n">
-        <v>2.4099</v>
+        <v>2.0764</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0211</v>
+        <v>0.0042</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6119</v>
+        <v>0.1218</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.7</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.3328</v>
       </c>
       <c r="J21" t="n">
-        <v>-14.9234</v>
+        <v>-9.651199999999999</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>2.53</v>
       </c>
       <c r="I22" t="n">
-        <v>2.3259</v>
+        <v>1.8681</v>
       </c>
       <c r="J22" t="n">
-        <v>41.8662</v>
+        <v>33.6258</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.25</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5322</v>
+        <v>0.6394</v>
       </c>
       <c r="J23" t="n">
-        <v>9.579599999999999</v>
+        <v>11.5092</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.2</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4145</v>
+        <v>0.5188</v>
       </c>
       <c r="J24" t="n">
-        <v>7.461</v>
+        <v>9.3384</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.05</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0171</v>
+        <v>0.1046</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3078</v>
+        <v>1.8828</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1831</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>-3.2958</v>
+        <v>-1.7316</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>0.91</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0905</v>
+        <v>-0.0939</v>
       </c>
       <c r="J27" t="n">
-        <v>-1.629</v>
+        <v>-1.6902</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.87</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.16</v>
+        <v>-0.1398</v>
       </c>
       <c r="J28" t="n">
-        <v>-2.88</v>
+        <v>-2.5164</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.77</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3403</v>
+        <v>-0.241</v>
       </c>
       <c r="J29" t="n">
-        <v>-6.1254</v>
+        <v>-4.338</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.72</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.428</v>
+        <v>-0.2877</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.704</v>
+        <v>-5.1786</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.59</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6135</v>
+        <v>-0.4099</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.043</v>
+        <v>-7.3782</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.43</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.6277</v>
       </c>
       <c r="J32" t="n">
-        <v>13.558</v>
+        <v>12.554</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.13</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2731</v>
+        <v>0.303</v>
       </c>
       <c r="J33" t="n">
-        <v>5.462</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.03</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0858</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>1.716</v>
+        <v>1.798</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.87</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2809</v>
+        <v>-0.1682</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.618</v>
+        <v>-3.364</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.6</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6475</v>
+        <v>-0.4305</v>
       </c>
       <c r="J36" t="n">
-        <v>-12.95</v>
+        <v>-8.609999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.47</v>
       </c>
       <c r="I37" t="n">
-        <v>1.1716</v>
+        <v>0.834</v>
       </c>
       <c r="J37" t="n">
-        <v>23.432</v>
+        <v>16.68</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.3</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8034</v>
+        <v>0.6081</v>
       </c>
       <c r="J38" t="n">
-        <v>16.068</v>
+        <v>12.162</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.22</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6057</v>
+        <v>0.4972</v>
       </c>
       <c r="J39" t="n">
-        <v>12.114</v>
+        <v>9.944000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.17</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4512</v>
+        <v>0.4266</v>
       </c>
       <c r="J40" t="n">
-        <v>9.023999999999999</v>
+        <v>8.532</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.74</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.8632</v>
+        <v>-0.822</v>
       </c>
       <c r="J41" t="n">
-        <v>-17.264</v>
+        <v>-16.44</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.15</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3434</v>
+        <v>0.3595</v>
       </c>
       <c r="J42" t="n">
-        <v>8.2416</v>
+        <v>8.628</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.02</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1105</v>
+        <v>0.0878</v>
       </c>
       <c r="J43" t="n">
-        <v>2.652</v>
+        <v>2.1072</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.96</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0553</v>
+        <v>-0.0548</v>
       </c>
       <c r="J44" t="n">
-        <v>-1.3272</v>
+        <v>-1.3152</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.9</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1858</v>
+        <v>-0.1247</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.4592</v>
+        <v>-2.9928</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.5</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.7519</v>
+        <v>-0.5101</v>
       </c>
       <c r="J46" t="n">
-        <v>-18.0456</v>
+        <v>-12.2424</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.47</v>
       </c>
       <c r="I47" t="n">
-        <v>1.1576</v>
+        <v>0.8273</v>
       </c>
       <c r="J47" t="n">
-        <v>27.7824</v>
+        <v>19.8552</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.37</v>
       </c>
       <c r="I48" t="n">
-        <v>0.9464</v>
+        <v>0.697</v>
       </c>
       <c r="J48" t="n">
-        <v>22.7136</v>
+        <v>16.728</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.27</v>
       </c>
       <c r="I49" t="n">
-        <v>0.7147</v>
+        <v>0.5627</v>
       </c>
       <c r="J49" t="n">
-        <v>17.1528</v>
+        <v>13.5048</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.05</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0801</v>
+        <v>0.1503</v>
       </c>
       <c r="J50" t="n">
-        <v>1.9224</v>
+        <v>3.6072</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.88</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5325</v>
+        <v>-0.4625</v>
       </c>
       <c r="J51" t="n">
-        <v>-12.78</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.21</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4212</v>
+        <v>0.4207</v>
       </c>
       <c r="J52" t="n">
-        <v>12.636</v>
+        <v>12.621</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.93</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1414</v>
+        <v>-0.0939</v>
       </c>
       <c r="J53" t="n">
-        <v>-4.242</v>
+        <v>-2.817</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.92</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1634</v>
+        <v>-0.1051</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.902</v>
+        <v>-3.153</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.86</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2724</v>
+        <v>-0.1698</v>
       </c>
       <c r="J55" t="n">
-        <v>-8.172000000000001</v>
+        <v>-5.094</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.75</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4387</v>
+        <v>-0.2804</v>
       </c>
       <c r="J56" t="n">
-        <v>-13.161</v>
+        <v>-8.412000000000001</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.37</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9781</v>
+        <v>0.7095</v>
       </c>
       <c r="J57" t="n">
-        <v>29.343</v>
+        <v>21.285</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.34</v>
       </c>
       <c r="I58" t="n">
-        <v>0.9122</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="J58" t="n">
-        <v>27.366</v>
+        <v>20.067</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.11</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2959</v>
+        <v>0.3367</v>
       </c>
       <c r="J59" t="n">
-        <v>8.877000000000001</v>
+        <v>10.101</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.04</v>
       </c>
       <c r="I60" t="n">
-        <v>0.0733</v>
+        <v>0.1322</v>
       </c>
       <c r="J60" t="n">
-        <v>2.199</v>
+        <v>3.966</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.88</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5145</v>
+        <v>-0.4473</v>
       </c>
       <c r="J61" t="n">
-        <v>-15.435</v>
+        <v>-13.419</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.2</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4573</v>
+        <v>0.448</v>
       </c>
       <c r="J62" t="n">
-        <v>8.231400000000001</v>
+        <v>8.064</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.85</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.2105</v>
+        <v>-0.1666</v>
       </c>
       <c r="J63" t="n">
-        <v>-3.789</v>
+        <v>-2.9988</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.83</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2458</v>
+        <v>-0.187</v>
       </c>
       <c r="J64" t="n">
-        <v>-4.4244</v>
+        <v>-3.366</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.63</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.5688</v>
+        <v>-0.3772</v>
       </c>
       <c r="J65" t="n">
-        <v>-10.2384</v>
+        <v>-6.7896</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.51</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.723</v>
+        <v>-0.4887</v>
       </c>
       <c r="J66" t="n">
-        <v>-13.014</v>
+        <v>-8.7966</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>2.44</v>
       </c>
       <c r="I67" t="n">
-        <v>2.2731</v>
+        <v>1.9031</v>
       </c>
       <c r="J67" t="n">
-        <v>40.9158</v>
+        <v>34.2558</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.59</v>
       </c>
       <c r="I68" t="n">
-        <v>1.3061</v>
+        <v>0.9388</v>
       </c>
       <c r="J68" t="n">
-        <v>23.5098</v>
+        <v>16.8984</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.05</v>
       </c>
       <c r="I69" t="n">
-        <v>0.0191</v>
+        <v>0.1063</v>
       </c>
       <c r="J69" t="n">
-        <v>0.3438</v>
+        <v>1.9134</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.97</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3156</v>
+        <v>-0.2276</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.6808</v>
+        <v>-4.0968</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4115</v>
+        <v>-0.3278</v>
       </c>
       <c r="J71" t="n">
-        <v>-7.407</v>
+        <v>-5.9004</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.51</v>
       </c>
       <c r="I72" t="n">
-        <v>1.3049</v>
+        <v>0.9162</v>
       </c>
       <c r="J72" t="n">
-        <v>30.0127</v>
+        <v>21.0726</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.38</v>
       </c>
       <c r="I73" t="n">
-        <v>1.0373</v>
+        <v>0.7412</v>
       </c>
       <c r="J73" t="n">
-        <v>23.8579</v>
+        <v>17.0476</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.02</v>
       </c>
       <c r="I74" t="n">
-        <v>0.0369</v>
+        <v>0.0781</v>
       </c>
       <c r="J74" t="n">
-        <v>0.8487</v>
+        <v>1.7963</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.88</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4896</v>
+        <v>-0.4282</v>
       </c>
       <c r="J75" t="n">
-        <v>-11.2608</v>
+        <v>-9.848599999999999</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.6</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.1415</v>
+        <v>-1.1351</v>
       </c>
       <c r="J76" t="n">
-        <v>-26.2545</v>
+        <v>-26.1073</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.56</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8101</v>
+        <v>0.7371</v>
       </c>
       <c r="J77" t="n">
-        <v>18.6323</v>
+        <v>16.9533</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.13</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2523</v>
+        <v>0.2907</v>
       </c>
       <c r="J78" t="n">
-        <v>5.8029</v>
+        <v>6.6861</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.13</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2523</v>
+        <v>0.2907</v>
       </c>
       <c r="J79" t="n">
-        <v>5.8029</v>
+        <v>6.6861</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.8</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3976</v>
+        <v>-0.2464</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.1448</v>
+        <v>-5.6672</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.71</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5185</v>
+        <v>-0.3339</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.9255</v>
+        <v>-7.6797</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>2.12</v>
       </c>
       <c r="I82" t="n">
-        <v>2.0053</v>
+        <v>1.5553</v>
       </c>
       <c r="J82" t="n">
-        <v>32.0848</v>
+        <v>24.8848</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.93</v>
       </c>
       <c r="I83" t="n">
-        <v>1.8337</v>
+        <v>1.3398</v>
       </c>
       <c r="J83" t="n">
-        <v>29.3392</v>
+        <v>21.4368</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.14</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2746</v>
+        <v>0.3557</v>
       </c>
       <c r="J84" t="n">
-        <v>4.3936</v>
+        <v>5.6912</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.92</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4656</v>
+        <v>-0.3855</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.4496</v>
+        <v>-6.168</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.79</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.7896</v>
+        <v>-0.7388</v>
       </c>
       <c r="J86" t="n">
-        <v>-12.6336</v>
+        <v>-11.8208</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.69</v>
       </c>
       <c r="I87" t="n">
-        <v>1.0463</v>
+        <v>0.9639</v>
       </c>
       <c r="J87" t="n">
-        <v>16.7408</v>
+        <v>15.4224</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.75</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.4009</v>
+        <v>-0.265</v>
       </c>
       <c r="J88" t="n">
-        <v>-6.4144</v>
+        <v>-4.24</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.74</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.4163</v>
+        <v>-0.2746</v>
       </c>
       <c r="J89" t="n">
-        <v>-6.6608</v>
+        <v>-4.3936</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.57</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.6503</v>
+        <v>-0.4349</v>
       </c>
       <c r="J90" t="n">
-        <v>-10.4048</v>
+        <v>-6.9584</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.33</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.9361</v>
+        <v>-0.6539</v>
       </c>
       <c r="J91" t="n">
-        <v>-14.9776</v>
+        <v>-10.4624</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.31</v>
       </c>
       <c r="I92" t="n">
-        <v>0.8467</v>
+        <v>0.6287</v>
       </c>
       <c r="J92" t="n">
-        <v>24.5543</v>
+        <v>18.2323</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.3</v>
       </c>
       <c r="I93" t="n">
-        <v>0.8237</v>
+        <v>0.6149</v>
       </c>
       <c r="J93" t="n">
-        <v>23.8873</v>
+        <v>17.8321</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.13</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3609</v>
+        <v>0.3706</v>
       </c>
       <c r="J94" t="n">
-        <v>10.4661</v>
+        <v>10.7474</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.05</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1096</v>
+        <v>0.1661</v>
       </c>
       <c r="J95" t="n">
-        <v>3.1784</v>
+        <v>4.8169</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.93</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3712</v>
+        <v>-0.2995</v>
       </c>
       <c r="J96" t="n">
-        <v>-10.7648</v>
+        <v>-8.685499999999999</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.28</v>
       </c>
       <c r="I97" t="n">
-        <v>0.5105</v>
+        <v>0.4916</v>
       </c>
       <c r="J97" t="n">
-        <v>14.8045</v>
+        <v>14.2564</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.08</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2116</v>
+        <v>0.2174</v>
       </c>
       <c r="J98" t="n">
-        <v>6.1364</v>
+        <v>6.3046</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.05</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1557</v>
+        <v>0.1505</v>
       </c>
       <c r="J99" t="n">
-        <v>4.5153</v>
+        <v>4.3645</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.79</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3862</v>
+        <v>-0.2433</v>
       </c>
       <c r="J100" t="n">
-        <v>-11.1998</v>
+        <v>-7.0557</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6872</v>
+        <v>-0.4606</v>
       </c>
       <c r="J101" t="n">
-        <v>-19.9288</v>
+        <v>-13.3574</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.39</v>
       </c>
       <c r="I102" t="n">
-        <v>1.0414</v>
+        <v>0.7459</v>
       </c>
       <c r="J102" t="n">
-        <v>36.449</v>
+        <v>26.1065</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.34</v>
       </c>
       <c r="I103" t="n">
-        <v>0.9328</v>
+        <v>0.6777</v>
       </c>
       <c r="J103" t="n">
-        <v>32.648</v>
+        <v>23.7195</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.03</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0571</v>
+        <v>0.107</v>
       </c>
       <c r="J104" t="n">
-        <v>1.9985</v>
+        <v>3.745</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.96</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2611</v>
+        <v>-0.1935</v>
       </c>
       <c r="J105" t="n">
-        <v>-9.138500000000001</v>
+        <v>-6.7725</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.83</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6318</v>
+        <v>-0.5737</v>
       </c>
       <c r="J106" t="n">
-        <v>-22.113</v>
+        <v>-20.0795</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.07</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1768</v>
+        <v>0.185</v>
       </c>
       <c r="J107" t="n">
-        <v>6.188</v>
+        <v>6.475</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.02</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0713</v>
+        <v>0.067</v>
       </c>
       <c r="J108" t="n">
-        <v>2.4955</v>
+        <v>2.345</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.02</v>
       </c>
       <c r="I109" t="n">
-        <v>0.0713</v>
+        <v>0.067</v>
       </c>
       <c r="J109" t="n">
-        <v>2.4955</v>
+        <v>2.345</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.97</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.0893</v>
+        <v>-0.0495</v>
       </c>
       <c r="J110" t="n">
-        <v>-3.1255</v>
+        <v>-1.7325</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.89</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2429</v>
+        <v>-0.1446</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.5015</v>
+        <v>-5.061</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.59</v>
       </c>
       <c r="I112" t="n">
-        <v>1.379</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="J112" t="n">
-        <v>33.096</v>
+        <v>23.3112</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.34</v>
       </c>
       <c r="I113" t="n">
-        <v>0.8617</v>
+        <v>0.6518</v>
       </c>
       <c r="J113" t="n">
-        <v>20.6808</v>
+        <v>15.6432</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.26</v>
       </c>
       <c r="I114" t="n">
-        <v>0.6661</v>
+        <v>0.5453</v>
       </c>
       <c r="J114" t="n">
-        <v>15.9864</v>
+        <v>13.0872</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.14</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3286</v>
+        <v>0.3743</v>
       </c>
       <c r="J115" t="n">
-        <v>7.8864</v>
+        <v>8.9832</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.87</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5673</v>
+        <v>-0.4981</v>
       </c>
       <c r="J116" t="n">
-        <v>-13.6152</v>
+        <v>-11.9544</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.35</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6028</v>
+        <v>0.5658</v>
       </c>
       <c r="J117" t="n">
-        <v>14.4672</v>
+        <v>13.5792</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.22</v>
       </c>
       <c r="I118" t="n">
-        <v>0.431</v>
+        <v>0.4288</v>
       </c>
       <c r="J118" t="n">
-        <v>10.344</v>
+        <v>10.2912</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.128</v>
+        <v>-0.0832</v>
       </c>
       <c r="J119" t="n">
-        <v>-3.072</v>
+        <v>-1.9968</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.67</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.5491</v>
+        <v>-0.3583</v>
       </c>
       <c r="J120" t="n">
-        <v>-13.1784</v>
+        <v>-8.5992</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.55</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6983</v>
+        <v>-0.4691</v>
       </c>
       <c r="J121" t="n">
-        <v>-16.7592</v>
+        <v>-11.2584</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.3</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8394</v>
+        <v>0.6209</v>
       </c>
       <c r="J122" t="n">
-        <v>24.3426</v>
+        <v>18.0061</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.18</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5436</v>
+        <v>0.4484</v>
       </c>
       <c r="J123" t="n">
-        <v>15.7644</v>
+        <v>13.0036</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.17</v>
       </c>
       <c r="I124" t="n">
-        <v>0.5163</v>
+        <v>0.4335</v>
       </c>
       <c r="J124" t="n">
-        <v>14.9727</v>
+        <v>12.5715</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.06</v>
       </c>
       <c r="I125" t="n">
-        <v>0.159</v>
+        <v>0.2044</v>
       </c>
       <c r="J125" t="n">
-        <v>4.611</v>
+        <v>5.9276</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.87</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5306</v>
+        <v>-0.4667</v>
       </c>
       <c r="J126" t="n">
-        <v>-15.3874</v>
+        <v>-13.5343</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.51</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7488</v>
+        <v>0.6865</v>
       </c>
       <c r="J127" t="n">
-        <v>21.7152</v>
+        <v>19.9085</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.38</v>
       </c>
       <c r="I128" t="n">
-        <v>0.5949</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="J128" t="n">
-        <v>17.2521</v>
+        <v>16.327</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.16</v>
       </c>
       <c r="I129" t="n">
-        <v>0.2944</v>
+        <v>0.3379</v>
       </c>
       <c r="J129" t="n">
-        <v>8.537599999999999</v>
+        <v>9.799099999999999</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3865</v>
+        <v>-0.2381</v>
       </c>
       <c r="J130" t="n">
-        <v>-11.2085</v>
+        <v>-6.9049</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.55</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.7151</v>
+        <v>-0.4821</v>
       </c>
       <c r="J131" t="n">
-        <v>-20.7379</v>
+        <v>-13.9809</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.55</v>
       </c>
       <c r="I132" t="n">
-        <v>1.3259</v>
+        <v>0.9341</v>
       </c>
       <c r="J132" t="n">
-        <v>27.8439</v>
+        <v>19.6161</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.45</v>
       </c>
       <c r="I133" t="n">
-        <v>1.1256</v>
+        <v>0.8056</v>
       </c>
       <c r="J133" t="n">
-        <v>23.6376</v>
+        <v>16.9176</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.07</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1513</v>
+        <v>0.2173</v>
       </c>
       <c r="J134" t="n">
-        <v>3.1773</v>
+        <v>4.5633</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.06</v>
       </c>
       <c r="I135" t="n">
-        <v>0.12</v>
+        <v>0.1866</v>
       </c>
       <c r="J135" t="n">
-        <v>2.52</v>
+        <v>3.9186</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.82</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.6794</v>
+        <v>-0.6206</v>
       </c>
       <c r="J136" t="n">
-        <v>-14.2674</v>
+        <v>-13.0326</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.22</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4282</v>
+        <v>0.427</v>
       </c>
       <c r="J137" t="n">
-        <v>8.9922</v>
+        <v>8.967000000000001</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.2</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3998</v>
+        <v>0.4051</v>
       </c>
       <c r="J138" t="n">
-        <v>8.395799999999999</v>
+        <v>8.507099999999999</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.08</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2109</v>
+        <v>0.2169</v>
       </c>
       <c r="J139" t="n">
-        <v>4.4289</v>
+        <v>4.5549</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.65</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.5763</v>
+        <v>-0.378</v>
       </c>
       <c r="J140" t="n">
-        <v>-12.1023</v>
+        <v>-7.938</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.62</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6141</v>
+        <v>-0.4059</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.8961</v>
+        <v>-8.523899999999999</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.96</v>
       </c>
       <c r="I142" t="n">
-        <v>1.8591</v>
+        <v>1.3714</v>
       </c>
       <c r="J142" t="n">
-        <v>31.6047</v>
+        <v>23.3138</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.49</v>
       </c>
       <c r="I143" t="n">
-        <v>1.1084</v>
+        <v>0.8196</v>
       </c>
       <c r="J143" t="n">
-        <v>18.8428</v>
+        <v>13.9332</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.31</v>
       </c>
       <c r="I144" t="n">
-        <v>0.6777</v>
+        <v>0.597</v>
       </c>
       <c r="J144" t="n">
-        <v>11.5209</v>
+        <v>10.149</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.26</v>
       </c>
       <c r="I145" t="n">
-        <v>0.5617</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="J145" t="n">
-        <v>9.5489</v>
+        <v>9.004899999999999</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.93</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4392</v>
+        <v>-0.3573</v>
       </c>
       <c r="J146" t="n">
-        <v>-7.4664</v>
+        <v>-6.0741</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>0.93</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.0256</v>
+        <v>-0.0533</v>
       </c>
       <c r="J147" t="n">
-        <v>-0.4352</v>
+        <v>-0.9061</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.74</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.3432</v>
+        <v>-0.2621</v>
       </c>
       <c r="J148" t="n">
-        <v>-5.8344</v>
+        <v>-4.4557</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.4422</v>
+        <v>-0.3073</v>
       </c>
       <c r="J149" t="n">
-        <v>-7.5174</v>
+        <v>-5.2241</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.63</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.5368000000000001</v>
+        <v>-0.3628</v>
       </c>
       <c r="J150" t="n">
-        <v>-9.1256</v>
+        <v>-6.1676</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6354</v>
+        <v>-0.4283</v>
       </c>
       <c r="J151" t="n">
-        <v>-10.8018</v>
+        <v>-7.2811</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7910/event_7910_evp_summary.xlsx
+++ b/database/event/7910/event_7910_evp_summary.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.7639</v>
+        <v>8.269399999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>3.998</v>
+        <v>3.7724</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3184</v>
+        <v>3.1402</v>
       </c>
       <c r="E2" t="n">
-        <v>8.7639</v>
+        <v>8.269399999999999</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>8.7639</v>
+        <v>8.269399999999999</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>6.2807</v>
+        <v>6.5003</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>158</v>
       </c>
       <c r="M2" t="n">
-        <v>6.2807</v>
+        <v>6.5003</v>
       </c>
       <c r="N2" t="n">
         <v>158</v>
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.7659</v>
+        <v>3.5796</v>
       </c>
       <c r="C3" t="n">
-        <v>1.718</v>
+        <v>1.633</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0621</v>
+        <v>1.0053</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7659</v>
+        <v>3.5796</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7659</v>
+        <v>3.5796</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6989</v>
+        <v>2.8138</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>158</v>
       </c>
       <c r="M3" t="n">
-        <v>2.6989</v>
+        <v>2.8138</v>
       </c>
       <c r="N3" t="n">
         <v>158</v>
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.4799</v>
+        <v>3.4926</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5875</v>
+        <v>1.5933</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9657</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4799</v>
+        <v>3.4926</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4799</v>
+        <v>3.4926</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4939</v>
+        <v>2.7454</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>86</v>
       </c>
       <c r="M4" t="n">
-        <v>2.4939</v>
+        <v>2.7454</v>
       </c>
       <c r="N4" t="n">
         <v>86</v>
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.3171</v>
+        <v>3.2356</v>
       </c>
       <c r="C5" t="n">
-        <v>1.5132</v>
+        <v>1.476</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8595</v>
+        <v>0.8487</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3171</v>
+        <v>3.2356</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3171</v>
+        <v>3.2356</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3773</v>
+        <v>2.5434</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>158</v>
       </c>
       <c r="M5" t="n">
-        <v>2.3773</v>
+        <v>2.5434</v>
       </c>
       <c r="N5" t="n">
         <v>158</v>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.0134</v>
+        <v>3.1342</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3747</v>
+        <v>1.4298</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7224</v>
+        <v>0.8025</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0134</v>
+        <v>3.1342</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3.0134</v>
+        <v>3.1342</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1596</v>
+        <v>2.4637</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>158</v>
       </c>
       <c r="M6" t="n">
-        <v>2.1596</v>
+        <v>2.4637</v>
       </c>
       <c r="N6" t="n">
         <v>158</v>
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.8905</v>
+        <v>2.9861</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3186</v>
+        <v>1.3622</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6669</v>
+        <v>0.7351</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8905</v>
+        <v>2.9861</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.8905</v>
+        <v>2.9861</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0715</v>
+        <v>2.3473</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>168</v>
       </c>
       <c r="M7" t="n">
-        <v>2.0715</v>
+        <v>2.3473</v>
       </c>
       <c r="N7" t="n">
         <v>168</v>
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.8034</v>
+        <v>2.8439</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2789</v>
+        <v>1.2974</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6276</v>
+        <v>0.6704</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8034</v>
+        <v>2.8439</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8034</v>
+        <v>2.8439</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.0091</v>
+        <v>2.2355</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>168</v>
       </c>
       <c r="M8" t="n">
-        <v>2.0091</v>
+        <v>2.2355</v>
       </c>
       <c r="N8" t="n">
         <v>168</v>
@@ -818,22 +818,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.8502</v>
+        <v>1.8576</v>
       </c>
       <c r="C9" t="n">
-        <v>0.844</v>
+        <v>0.8474</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1973</v>
+        <v>0.2214</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8502</v>
+        <v>1.8576</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8502</v>
+        <v>1.8576</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.326</v>
+        <v>1.4602</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>108</v>
       </c>
       <c r="M9" t="n">
-        <v>1.326</v>
+        <v>1.4602</v>
       </c>
       <c r="N9" t="n">
         <v>108</v>
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.8249</v>
+        <v>1.8012</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8325</v>
+        <v>0.8217</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1858</v>
+        <v>0.1957</v>
       </c>
       <c r="E10" t="n">
-        <v>1.8249</v>
+        <v>1.8012</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8249</v>
+        <v>1.8012</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3078</v>
+        <v>1.4159</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>86</v>
       </c>
       <c r="M10" t="n">
-        <v>1.3078</v>
+        <v>1.4159</v>
       </c>
       <c r="N10" t="n">
         <v>86</v>
@@ -910,22 +910,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.8091</v>
+        <v>1.7577</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8253</v>
+        <v>0.8018</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1787</v>
+        <v>0.1759</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8091</v>
+        <v>1.7577</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8091</v>
+        <v>1.7577</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -934,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2965</v>
+        <v>1.3817</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>108</v>
       </c>
       <c r="M11" t="n">
-        <v>1.2965</v>
+        <v>1.3817</v>
       </c>
       <c r="N11" t="n">
         <v>108</v>
@@ -956,22 +956,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.7506</v>
+        <v>1.7242</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7986</v>
+        <v>0.7866</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1523</v>
+        <v>0.1607</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7506</v>
+        <v>1.7242</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1.7506</v>
+        <v>1.7242</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.2546</v>
+        <v>1.3553</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>39</v>
       </c>
       <c r="M12" t="n">
-        <v>1.2546</v>
+        <v>1.3553</v>
       </c>
       <c r="N12" t="n">
         <v>39</v>
@@ -1002,22 +1002,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.5731</v>
+        <v>1.5908</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7176</v>
+        <v>0.7257</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0722</v>
+        <v>0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5731</v>
+        <v>1.5908</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.5731</v>
+        <v>1.5908</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1274</v>
+        <v>1.2505</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>86</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1274</v>
+        <v>1.2505</v>
       </c>
       <c r="N13" t="n">
         <v>86</v>
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.5562</v>
+        <v>1.577</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7099</v>
+        <v>0.7194</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0645</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5562</v>
+        <v>1.577</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5562</v>
+        <v>1.577</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1153</v>
+        <v>1.2396</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>53</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1153</v>
+        <v>1.2396</v>
       </c>
       <c r="N14" t="n">
         <v>53</v>
@@ -1094,22 +1094,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.4907</v>
+        <v>1.5305</v>
       </c>
       <c r="C15" t="n">
-        <v>0.68</v>
+        <v>0.6982</v>
       </c>
       <c r="D15" t="n">
-        <v>0.035</v>
+        <v>0.0725</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4907</v>
+        <v>1.5305</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4907</v>
+        <v>1.5305</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0683</v>
+        <v>1.2031</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>168</v>
       </c>
       <c r="M15" t="n">
-        <v>1.0683</v>
+        <v>1.2031</v>
       </c>
       <c r="N15" t="n">
         <v>168</v>
@@ -1136,26 +1136,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.261</v>
+        <v>1.2711</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5753</v>
+        <v>0.5799</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0687</v>
+        <v>-0.0456</v>
       </c>
       <c r="E16" t="n">
-        <v>1.261</v>
+        <v>1.2711</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.261</v>
+        <v>1.2711</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1164,44 +1164,44 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9036999999999999</v>
+        <v>0.9992</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9036999999999999</v>
+        <v>0.9992</v>
       </c>
       <c r="N16" t="n">
-        <v>53</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.1907</v>
+        <v>1.2416</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5432</v>
+        <v>0.5664</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1005</v>
+        <v>-0.059</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1907</v>
+        <v>1.2416</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1907</v>
+        <v>1.2416</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1210,19 +1210,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.976</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.976</v>
       </c>
       <c r="N17" t="n">
-        <v>108</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.888</v>
+        <v>0.9619</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4051</v>
+        <v>0.4388</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2371</v>
+        <v>-0.1863</v>
       </c>
       <c r="E18" t="n">
-        <v>0.888</v>
+        <v>0.9619</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.888</v>
+        <v>0.9619</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6364</v>
+        <v>0.7561</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>168</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6364</v>
+        <v>0.7561</v>
       </c>
       <c r="N18" t="n">
         <v>168</v>
@@ -1278,22 +1278,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7794</v>
+        <v>0.7849</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3556</v>
+        <v>0.3581</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2862</v>
+        <v>-0.2669</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7794</v>
+        <v>0.7849</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7794</v>
+        <v>0.7849</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5586</v>
+        <v>0.617</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>64</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5586</v>
+        <v>0.617</v>
       </c>
       <c r="N19" t="n">
         <v>64</v>
@@ -1324,22 +1324,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6454</v>
+        <v>0.6773</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2944</v>
+        <v>0.309</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3466</v>
+        <v>-0.3159</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6454</v>
+        <v>0.6773</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6454</v>
+        <v>0.6773</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4625</v>
+        <v>0.5324</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>39</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4625</v>
+        <v>0.5324</v>
       </c>
       <c r="N20" t="n">
         <v>39</v>
@@ -1366,26 +1366,26 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.3035</v>
+        <v>0.3717</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1385</v>
+        <v>0.1696</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.501</v>
+        <v>-0.455</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3035</v>
+        <v>0.3717</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3035</v>
+        <v>0.3717</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1394,19 +1394,19 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2175</v>
+        <v>0.2922</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>64</v>
+        <v>158</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2175</v>
+        <v>0.2922</v>
       </c>
       <c r="N21" t="n">
-        <v>64</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22">
@@ -1416,22 +1416,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2856</v>
+        <v>0.3309</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1303</v>
+        <v>0.151</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5091</v>
+        <v>-0.4736</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2856</v>
+        <v>0.3309</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2856</v>
+        <v>0.3309</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2047</v>
+        <v>0.2601</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>53</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2047</v>
+        <v>0.2601</v>
       </c>
       <c r="N22" t="n">
         <v>53</v>
@@ -1458,26 +1458,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2538</v>
+        <v>0.2926</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1158</v>
+        <v>0.1335</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5234</v>
+        <v>-0.491</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2538</v>
+        <v>0.2926</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2538</v>
+        <v>0.2926</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1486,19 +1486,19 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1819</v>
+        <v>0.23</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>158</v>
+        <v>64</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1819</v>
+        <v>0.23</v>
       </c>
       <c r="N23" t="n">
-        <v>158</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24">
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2343</v>
+        <v>0.2083</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1069</v>
+        <v>0.095</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5322</v>
+        <v>-0.5294</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2343</v>
+        <v>0.2083</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2343</v>
+        <v>0.2083</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1532,7 +1532,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1679</v>
+        <v>0.1637</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>64</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1679</v>
+        <v>0.1637</v>
       </c>
       <c r="N24" t="n">
         <v>64</v>
@@ -1554,22 +1554,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.059</v>
+        <v>0.078</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0269</v>
+        <v>0.0356</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.5887</v>
       </c>
       <c r="E25" t="n">
-        <v>0.059</v>
+        <v>0.078</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.059</v>
+        <v>0.078</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0423</v>
+        <v>0.0613</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>38</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0423</v>
+        <v>0.0613</v>
       </c>
       <c r="N25" t="n">
         <v>38</v>
@@ -1596,26 +1596,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0359</v>
+        <v>0.0336</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0164</v>
+        <v>0.0153</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6218</v>
+        <v>-0.6089</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0359</v>
+        <v>0.0336</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0359</v>
+        <v>0.0336</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1624,44 +1624,44 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0257</v>
+        <v>0.0264</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0257</v>
+        <v>0.0264</v>
       </c>
       <c r="N26" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0018</v>
+        <v>0.0197</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6388</v>
+        <v>-0.6152</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0018</v>
+        <v>0.0197</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.0018</v>
+        <v>0.0197</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1670,44 +1670,44 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.0013</v>
+        <v>0.0155</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0013</v>
+        <v>0.0155</v>
       </c>
       <c r="N27" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0631</v>
+        <v>-0.0447</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0288</v>
+        <v>-0.0204</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6665</v>
+        <v>-0.6446</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0631</v>
+        <v>-0.0447</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.0631</v>
+        <v>-0.0447</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1716,44 +1716,44 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.0452</v>
+        <v>-0.0351</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>38</v>
+        <v>168</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0452</v>
+        <v>-0.0351</v>
       </c>
       <c r="N28" t="n">
-        <v>38</v>
+        <v>168</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1899</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0866</v>
+        <v>-0.0357</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7237</v>
+        <v>-0.6598000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1899</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.1899</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1762,19 +1762,19 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.1361</v>
+        <v>-0.0615</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>168</v>
+        <v>38</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1361</v>
+        <v>-0.0615</v>
       </c>
       <c r="N29" t="n">
-        <v>168</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30">
@@ -1784,22 +1784,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3846</v>
+        <v>-0.3504</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1755</v>
+        <v>-0.1598</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.8116</v>
+        <v>-0.7837</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.3846</v>
+        <v>-0.3504</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.3846</v>
+        <v>-0.3504</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1808,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.2756</v>
+        <v>-0.2754</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>64</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2756</v>
+        <v>-0.2754</v>
       </c>
       <c r="N30" t="n">
         <v>64</v>
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4483</v>
+        <v>-0.4388</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2045</v>
+        <v>-0.2002</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8404</v>
+        <v>-0.824</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4483</v>
+        <v>-0.4388</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.4483</v>
+        <v>-0.4388</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.3213</v>
+        <v>-0.3449</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>53</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3213</v>
+        <v>-0.3449</v>
       </c>
       <c r="N31" t="n">
         <v>53</v>
@@ -1876,22 +1876,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5413</v>
+        <v>-0.5286</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2469</v>
+        <v>-0.2411</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8824</v>
+        <v>-0.8648</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5413</v>
+        <v>-0.5286</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.5413</v>
+        <v>-0.5286</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.3879</v>
+        <v>-0.4155</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>64</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3879</v>
+        <v>-0.4155</v>
       </c>
       <c r="N32" t="n">
         <v>64</v>
@@ -1918,26 +1918,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6018</v>
+        <v>-0.5341</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2745</v>
+        <v>-0.2437</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9097</v>
+        <v>-0.8673</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6018</v>
+        <v>-0.5341</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.6018</v>
+        <v>-0.5341</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1946,19 +1946,19 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.4313</v>
+        <v>-0.4198</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4313</v>
+        <v>-0.4198</v>
       </c>
       <c r="N33" t="n">
-        <v>38</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34">
@@ -1968,22 +1968,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6677999999999999</v>
+        <v>-0.5452</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3046</v>
+        <v>-0.2487</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9395</v>
+        <v>-0.8724</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6677999999999999</v>
+        <v>-0.5452</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.6677999999999999</v>
+        <v>-0.5452</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.4786</v>
+        <v>-0.4286</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>108</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4786</v>
+        <v>-0.4286</v>
       </c>
       <c r="N34" t="n">
         <v>108</v>
@@ -2010,26 +2010,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7059</v>
+        <v>-0.5904</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.322</v>
+        <v>-0.2693</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9567</v>
+        <v>-0.893</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7059</v>
+        <v>-0.5904</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.7059</v>
+        <v>-0.5904</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2038,19 +2038,19 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.5059</v>
+        <v>-0.4641</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.5059</v>
+        <v>-0.4641</v>
       </c>
       <c r="N35" t="n">
-        <v>86</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36">
@@ -2060,22 +2060,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8001</v>
+        <v>-0.7228</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.365</v>
+        <v>-0.3297</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9992</v>
+        <v>-0.9532</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8001</v>
+        <v>-0.7228</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.8001</v>
+        <v>-0.7228</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.5734</v>
+        <v>-0.5682</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>108</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.5734</v>
+        <v>-0.5682</v>
       </c>
       <c r="N36" t="n">
         <v>108</v>
@@ -2106,22 +2106,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9952</v>
+        <v>-0.9448</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.454</v>
+        <v>-0.431</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0873</v>
+        <v>-1.0543</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9952</v>
+        <v>-0.9448</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.9952</v>
+        <v>-0.9448</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2130,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.7131999999999999</v>
+        <v>-0.7427</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>38</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7131999999999999</v>
+        <v>-0.7427</v>
       </c>
       <c r="N37" t="n">
         <v>38</v>
@@ -2152,22 +2152,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0728</v>
+        <v>-1.0054</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4894</v>
+        <v>-0.4587</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1223</v>
+        <v>-1.0819</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0728</v>
+        <v>-1.0054</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.0728</v>
+        <v>-1.0054</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.7688</v>
+        <v>-0.7903</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>39</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.7688</v>
+        <v>-0.7903</v>
       </c>
       <c r="N38" t="n">
         <v>39</v>
@@ -2198,22 +2198,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2562</v>
+        <v>-1.1569</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.5731000000000001</v>
+        <v>-0.5278</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2051</v>
+        <v>-1.1508</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2562</v>
+        <v>-1.1569</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.2562</v>
+        <v>-1.1569</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.9003</v>
+        <v>-0.9094</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>39</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.9003</v>
+        <v>-0.9094</v>
       </c>
       <c r="N39" t="n">
         <v>39</v>
@@ -2244,22 +2244,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3114</v>
+        <v>-1.1681</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5982</v>
+        <v>-0.5329</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.23</v>
+        <v>-1.1559</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3114</v>
+        <v>-1.1681</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.3114</v>
+        <v>-1.1681</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.9398</v>
+        <v>-0.9182</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>86</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.9398</v>
+        <v>-0.9182</v>
       </c>
       <c r="N40" t="n">
         <v>86</v>
@@ -2290,22 +2290,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.3273</v>
+        <v>-1.2244</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.6055</v>
+        <v>-0.5586</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2372</v>
+        <v>-1.1816</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.3273</v>
+        <v>-1.2244</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.3273</v>
+        <v>-1.2244</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.9512</v>
+        <v>-0.9625</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>53</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.9512</v>
+        <v>-0.9625</v>
       </c>
       <c r="N41" t="n">
         <v>53</v>
@@ -2429,10 +2429,10 @@
         <v>1.34</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9052</v>
+        <v>0.8474</v>
       </c>
       <c r="J2" t="n">
-        <v>21.7248</v>
+        <v>20.3376</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5718</v>
+        <v>0.5531</v>
       </c>
       <c r="J3" t="n">
-        <v>13.7232</v>
+        <v>13.2744</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.13</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3966</v>
+        <v>0.3939</v>
       </c>
       <c r="J4" t="n">
-        <v>9.5184</v>
+        <v>9.4536</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.06</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1987</v>
+        <v>0.2098</v>
       </c>
       <c r="J5" t="n">
-        <v>4.7688</v>
+        <v>5.0352</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.97</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1665</v>
+        <v>-0.1607</v>
       </c>
       <c r="J6" t="n">
-        <v>-3.996</v>
+        <v>-3.8568</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.13</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3402</v>
+        <v>0.3344</v>
       </c>
       <c r="J7" t="n">
-        <v>8.1648</v>
+        <v>8.025600000000001</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1424</v>
+        <v>0.1437</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4176</v>
+        <v>3.4488</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.02</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0902</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>2.1648</v>
+        <v>2.1792</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.68</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3429</v>
+        <v>-0.3564</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.2296</v>
+        <v>-8.553599999999999</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.62</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3992</v>
+        <v>-0.4104</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.5808</v>
+        <v>-9.849600000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.42</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0468</v>
+        <v>1.0001</v>
       </c>
       <c r="J12" t="n">
-        <v>30.3572</v>
+        <v>29.0029</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.18</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5185</v>
+        <v>0.506</v>
       </c>
       <c r="J13" t="n">
-        <v>15.0365</v>
+        <v>14.674</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.1</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3121</v>
+        <v>0.3169</v>
       </c>
       <c r="J14" t="n">
-        <v>9.0509</v>
+        <v>9.190099999999999</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.09</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2838</v>
+        <v>0.2906</v>
       </c>
       <c r="J15" t="n">
-        <v>8.2302</v>
+        <v>8.4274</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0379</v>
+        <v>-0.0261</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.0991</v>
+        <v>-0.7569</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.07</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1908</v>
+        <v>0.1968</v>
       </c>
       <c r="J17" t="n">
-        <v>5.5332</v>
+        <v>5.7072</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.06</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1687</v>
+        <v>0.1751</v>
       </c>
       <c r="J18" t="n">
-        <v>4.8923</v>
+        <v>5.0779</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.02</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0716</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>2.0764</v>
+        <v>2.2417</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0042</v>
+        <v>0.003</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1218</v>
+        <v>0.08699999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.7</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3328</v>
+        <v>-0.345</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.651199999999999</v>
+        <v>-10.005</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>2.53</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8681</v>
+        <v>1.8453</v>
       </c>
       <c r="J22" t="n">
-        <v>33.6258</v>
+        <v>33.2154</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.25</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6394</v>
+        <v>0.6244</v>
       </c>
       <c r="J23" t="n">
-        <v>11.5092</v>
+        <v>11.2392</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.2</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5188</v>
+        <v>0.5167</v>
       </c>
       <c r="J24" t="n">
-        <v>9.3384</v>
+        <v>9.300599999999999</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.05</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1046</v>
+        <v>0.1361</v>
       </c>
       <c r="J25" t="n">
-        <v>1.8828</v>
+        <v>2.4498</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.0669</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.7316</v>
+        <v>-1.2042</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>0.91</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0939</v>
+        <v>-0.113</v>
       </c>
       <c r="J27" t="n">
-        <v>-1.6902</v>
+        <v>-2.034</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.87</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1398</v>
+        <v>-0.1594</v>
       </c>
       <c r="J28" t="n">
-        <v>-2.5164</v>
+        <v>-2.8692</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.77</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.241</v>
+        <v>-0.2602</v>
       </c>
       <c r="J29" t="n">
-        <v>-4.338</v>
+        <v>-4.6836</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.72</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2877</v>
+        <v>-0.3061</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.1786</v>
+        <v>-5.5098</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.59</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4099</v>
+        <v>-0.4236</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.3782</v>
+        <v>-7.6248</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.43</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6277</v>
+        <v>0.6999</v>
       </c>
       <c r="J32" t="n">
-        <v>12.554</v>
+        <v>13.998</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.13</v>
       </c>
       <c r="I33" t="n">
-        <v>0.303</v>
+        <v>0.3073</v>
       </c>
       <c r="J33" t="n">
-        <v>6.06</v>
+        <v>6.146</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.03</v>
       </c>
       <c r="I34" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>1.798</v>
+        <v>1.972</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.87</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1682</v>
+        <v>-0.1813</v>
       </c>
       <c r="J35" t="n">
-        <v>-3.364</v>
+        <v>-3.626</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.6</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4305</v>
+        <v>-0.4382</v>
       </c>
       <c r="J36" t="n">
-        <v>-8.609999999999999</v>
+        <v>-8.763999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.47</v>
       </c>
       <c r="I37" t="n">
-        <v>0.834</v>
+        <v>0.9197</v>
       </c>
       <c r="J37" t="n">
-        <v>16.68</v>
+        <v>18.394</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.3</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6081</v>
+        <v>0.674</v>
       </c>
       <c r="J38" t="n">
-        <v>12.162</v>
+        <v>13.48</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.22</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4972</v>
+        <v>0.5507</v>
       </c>
       <c r="J39" t="n">
-        <v>9.944000000000001</v>
+        <v>11.014</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.17</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4266</v>
+        <v>0.4705</v>
       </c>
       <c r="J40" t="n">
-        <v>8.532</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.74</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.822</v>
+        <v>-0.756</v>
       </c>
       <c r="J41" t="n">
-        <v>-16.44</v>
+        <v>-15.12</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.15</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3595</v>
+        <v>0.3697</v>
       </c>
       <c r="J42" t="n">
-        <v>8.628</v>
+        <v>8.8728</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.02</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0878</v>
+        <v>0.0891</v>
       </c>
       <c r="J43" t="n">
-        <v>2.1072</v>
+        <v>2.1384</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.96</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0548</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>-1.3152</v>
+        <v>-1.5864</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.9</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1247</v>
+        <v>-0.1396</v>
       </c>
       <c r="J45" t="n">
-        <v>-2.9928</v>
+        <v>-3.3504</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.5</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5101</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="J46" t="n">
-        <v>-12.2424</v>
+        <v>-12.3744</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.47</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8273</v>
+        <v>0.9139</v>
       </c>
       <c r="J47" t="n">
-        <v>19.8552</v>
+        <v>21.9336</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.37</v>
       </c>
       <c r="I48" t="n">
-        <v>0.697</v>
+        <v>0.7726</v>
       </c>
       <c r="J48" t="n">
-        <v>16.728</v>
+        <v>18.5424</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.27</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5627</v>
+        <v>0.6248</v>
       </c>
       <c r="J49" t="n">
-        <v>13.5048</v>
+        <v>14.9952</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.05</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1503</v>
+        <v>0.1681</v>
       </c>
       <c r="J50" t="n">
-        <v>3.6072</v>
+        <v>4.0344</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.88</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4625</v>
+        <v>-0.4337</v>
       </c>
       <c r="J51" t="n">
-        <v>-11.1</v>
+        <v>-10.4088</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.21</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4207</v>
+        <v>0.4603</v>
       </c>
       <c r="J52" t="n">
-        <v>12.621</v>
+        <v>13.809</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.93</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0939</v>
+        <v>-0.1068</v>
       </c>
       <c r="J53" t="n">
-        <v>-2.817</v>
+        <v>-3.204</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.92</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1051</v>
+        <v>-0.1186</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.153</v>
+        <v>-3.558</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.86</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1698</v>
+        <v>-0.185</v>
       </c>
       <c r="J55" t="n">
-        <v>-5.094</v>
+        <v>-5.55</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.75</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2804</v>
+        <v>-0.2947</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.412000000000001</v>
+        <v>-8.840999999999999</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.37</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7095</v>
+        <v>0.7836</v>
       </c>
       <c r="J57" t="n">
-        <v>21.285</v>
+        <v>23.508</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.34</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6689000000000001</v>
+        <v>0.7393</v>
       </c>
       <c r="J58" t="n">
-        <v>20.067</v>
+        <v>22.179</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.11</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3367</v>
+        <v>0.3439</v>
       </c>
       <c r="J59" t="n">
-        <v>10.101</v>
+        <v>10.317</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.04</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1322</v>
+        <v>0.1468</v>
       </c>
       <c r="J60" t="n">
-        <v>3.966</v>
+        <v>4.404</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.88</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4473</v>
+        <v>-0.423</v>
       </c>
       <c r="J61" t="n">
-        <v>-13.419</v>
+        <v>-12.69</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.2</v>
       </c>
       <c r="I62" t="n">
-        <v>0.448</v>
+        <v>0.4833</v>
       </c>
       <c r="J62" t="n">
-        <v>8.064</v>
+        <v>8.699400000000001</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.85</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.1666</v>
+        <v>-0.1851</v>
       </c>
       <c r="J63" t="n">
-        <v>-2.9988</v>
+        <v>-3.3318</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.83</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.187</v>
+        <v>-0.2056</v>
       </c>
       <c r="J64" t="n">
-        <v>-3.366</v>
+        <v>-3.7008</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.63</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3772</v>
+        <v>-0.3916</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.7896</v>
+        <v>-7.0488</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.51</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4887</v>
+        <v>-0.4973</v>
       </c>
       <c r="J66" t="n">
-        <v>-8.7966</v>
+        <v>-8.9514</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>2.44</v>
       </c>
       <c r="I67" t="n">
-        <v>1.9031</v>
+        <v>2.0481</v>
       </c>
       <c r="J67" t="n">
-        <v>34.2558</v>
+        <v>36.8658</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.59</v>
       </c>
       <c r="I68" t="n">
-        <v>0.9388</v>
+        <v>1.041</v>
       </c>
       <c r="J68" t="n">
-        <v>16.8984</v>
+        <v>18.738</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.05</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1063</v>
+        <v>0.1373</v>
       </c>
       <c r="J69" t="n">
-        <v>1.9134</v>
+        <v>2.4714</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.97</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2276</v>
+        <v>-0.2035</v>
       </c>
       <c r="J70" t="n">
-        <v>-4.0968</v>
+        <v>-3.663</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3278</v>
+        <v>-0.2995</v>
       </c>
       <c r="J71" t="n">
-        <v>-5.9004</v>
+        <v>-5.391</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.51</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9162</v>
+        <v>1.0023</v>
       </c>
       <c r="J72" t="n">
-        <v>21.0726</v>
+        <v>23.0529</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.38</v>
       </c>
       <c r="I73" t="n">
-        <v>0.7412</v>
+        <v>0.8143</v>
       </c>
       <c r="J73" t="n">
-        <v>17.0476</v>
+        <v>18.7289</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.02</v>
       </c>
       <c r="I74" t="n">
-        <v>0.0781</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="J74" t="n">
-        <v>1.7963</v>
+        <v>2.0447</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.88</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4282</v>
+        <v>-0.4097</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.848599999999999</v>
+        <v>-9.4231</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.6</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.1351</v>
+        <v>-1.0314</v>
       </c>
       <c r="J76" t="n">
-        <v>-26.1073</v>
+        <v>-23.7222</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.56</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7371</v>
+        <v>0.8246</v>
       </c>
       <c r="J77" t="n">
-        <v>16.9533</v>
+        <v>18.9658</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.13</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2907</v>
+        <v>0.2983</v>
       </c>
       <c r="J78" t="n">
-        <v>6.6861</v>
+        <v>6.8609</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.13</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2907</v>
+        <v>0.2983</v>
       </c>
       <c r="J79" t="n">
-        <v>6.6861</v>
+        <v>6.8609</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.8</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2464</v>
+        <v>-0.2582</v>
       </c>
       <c r="J80" t="n">
-        <v>-5.6672</v>
+        <v>-5.9386</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.71</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3339</v>
+        <v>-0.3441</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.6797</v>
+        <v>-7.9143</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>2.12</v>
       </c>
       <c r="I82" t="n">
-        <v>1.5553</v>
+        <v>1.6888</v>
       </c>
       <c r="J82" t="n">
-        <v>24.8848</v>
+        <v>27.0208</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.93</v>
       </c>
       <c r="I83" t="n">
-        <v>1.3398</v>
+        <v>1.4645</v>
       </c>
       <c r="J83" t="n">
-        <v>21.4368</v>
+        <v>23.432</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.14</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3557</v>
+        <v>0.3819</v>
       </c>
       <c r="J84" t="n">
-        <v>5.6912</v>
+        <v>6.1104</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.92</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3855</v>
+        <v>-0.3545</v>
       </c>
       <c r="J85" t="n">
-        <v>-6.168</v>
+        <v>-5.672</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.79</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.7388</v>
+        <v>-0.6751</v>
       </c>
       <c r="J86" t="n">
-        <v>-11.8208</v>
+        <v>-10.8016</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.69</v>
       </c>
       <c r="I87" t="n">
-        <v>0.9639</v>
+        <v>1.057</v>
       </c>
       <c r="J87" t="n">
-        <v>15.4224</v>
+        <v>16.912</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.75</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.265</v>
+        <v>-0.2828</v>
       </c>
       <c r="J88" t="n">
-        <v>-4.24</v>
+        <v>-4.5248</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.74</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2746</v>
+        <v>-0.2922</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.3936</v>
+        <v>-4.6752</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.57</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4349</v>
+        <v>-0.4462</v>
       </c>
       <c r="J90" t="n">
-        <v>-6.9584</v>
+        <v>-7.1392</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.33</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6539</v>
+        <v>-0.6512</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.4624</v>
+        <v>-10.4192</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.31</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6287</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="J92" t="n">
-        <v>18.2323</v>
+        <v>20.1579</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.3</v>
       </c>
       <c r="I93" t="n">
-        <v>0.6149</v>
+        <v>0.68</v>
       </c>
       <c r="J93" t="n">
-        <v>17.8321</v>
+        <v>19.72</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.13</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3706</v>
+        <v>0.3935</v>
       </c>
       <c r="J94" t="n">
-        <v>10.7474</v>
+        <v>11.4115</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.05</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1661</v>
+        <v>0.1791</v>
       </c>
       <c r="J95" t="n">
-        <v>4.8169</v>
+        <v>5.1939</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.93</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2995</v>
+        <v>-0.287</v>
       </c>
       <c r="J96" t="n">
-        <v>-8.685499999999999</v>
+        <v>-8.323</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.28</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4916</v>
+        <v>0.5429</v>
       </c>
       <c r="J97" t="n">
-        <v>14.2564</v>
+        <v>15.7441</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.08</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2174</v>
+        <v>0.2215</v>
       </c>
       <c r="J98" t="n">
-        <v>6.3046</v>
+        <v>6.4235</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.05</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1505</v>
+        <v>0.1559</v>
       </c>
       <c r="J99" t="n">
-        <v>4.3645</v>
+        <v>4.5211</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.79</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2433</v>
+        <v>-0.2578</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.0557</v>
+        <v>-7.4762</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4606</v>
+        <v>-0.468</v>
       </c>
       <c r="J101" t="n">
-        <v>-13.3574</v>
+        <v>-13.572</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.39</v>
       </c>
       <c r="I102" t="n">
-        <v>0.7459</v>
+        <v>0.8212</v>
       </c>
       <c r="J102" t="n">
-        <v>26.1065</v>
+        <v>28.742</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.34</v>
       </c>
       <c r="I103" t="n">
-        <v>0.6777</v>
+        <v>0.747</v>
       </c>
       <c r="J103" t="n">
-        <v>23.7195</v>
+        <v>26.145</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.03</v>
       </c>
       <c r="I104" t="n">
-        <v>0.107</v>
+        <v>0.1198</v>
       </c>
       <c r="J104" t="n">
-        <v>3.745</v>
+        <v>4.193</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.96</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1935</v>
+        <v>-0.189</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.7725</v>
+        <v>-6.615</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.83</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5737</v>
+        <v>-0.5392</v>
       </c>
       <c r="J106" t="n">
-        <v>-20.0795</v>
+        <v>-18.872</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.07</v>
       </c>
       <c r="I107" t="n">
-        <v>0.185</v>
+        <v>0.1926</v>
       </c>
       <c r="J107" t="n">
-        <v>6.475</v>
+        <v>6.741</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.02</v>
       </c>
       <c r="I108" t="n">
-        <v>0.067</v>
+        <v>0.0741</v>
       </c>
       <c r="J108" t="n">
-        <v>2.345</v>
+        <v>2.5935</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.02</v>
       </c>
       <c r="I109" t="n">
-        <v>0.067</v>
+        <v>0.0741</v>
       </c>
       <c r="J109" t="n">
-        <v>2.345</v>
+        <v>2.5935</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.97</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.0495</v>
+        <v>-0.0578</v>
       </c>
       <c r="J110" t="n">
-        <v>-1.7325</v>
+        <v>-2.023</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.89</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.1446</v>
+        <v>-0.1577</v>
       </c>
       <c r="J111" t="n">
-        <v>-5.061</v>
+        <v>-5.5195</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.59</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9713000000000001</v>
+        <v>1.0696</v>
       </c>
       <c r="J112" t="n">
-        <v>23.3112</v>
+        <v>25.6704</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.34</v>
       </c>
       <c r="I113" t="n">
-        <v>0.6518</v>
+        <v>0.7244</v>
       </c>
       <c r="J113" t="n">
-        <v>15.6432</v>
+        <v>17.3856</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.26</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5453</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="J114" t="n">
-        <v>13.0872</v>
+        <v>14.5536</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.14</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3743</v>
+        <v>0.4036</v>
       </c>
       <c r="J115" t="n">
-        <v>8.9832</v>
+        <v>9.686400000000001</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.87</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4981</v>
+        <v>-0.4645</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.9544</v>
+        <v>-11.148</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.35</v>
       </c>
       <c r="I117" t="n">
-        <v>0.5658</v>
+        <v>0.6268</v>
       </c>
       <c r="J117" t="n">
-        <v>13.5792</v>
+        <v>15.0432</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.22</v>
       </c>
       <c r="I118" t="n">
-        <v>0.4288</v>
+        <v>0.4706</v>
       </c>
       <c r="J118" t="n">
-        <v>10.2912</v>
+        <v>11.2944</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0832</v>
+        <v>-0.0953</v>
       </c>
       <c r="J119" t="n">
-        <v>-1.9968</v>
+        <v>-2.2872</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.67</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3583</v>
+        <v>-0.3702</v>
       </c>
       <c r="J120" t="n">
-        <v>-8.5992</v>
+        <v>-8.8848</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.55</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4691</v>
+        <v>-0.4761</v>
       </c>
       <c r="J121" t="n">
-        <v>-11.2584</v>
+        <v>-11.4264</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.3</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6209</v>
+        <v>0.6851</v>
       </c>
       <c r="J122" t="n">
-        <v>18.0061</v>
+        <v>19.8679</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.18</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4484</v>
+        <v>0.4933</v>
       </c>
       <c r="J123" t="n">
-        <v>13.0036</v>
+        <v>14.3057</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.17</v>
       </c>
       <c r="I124" t="n">
-        <v>0.4335</v>
+        <v>0.4764</v>
       </c>
       <c r="J124" t="n">
-        <v>12.5715</v>
+        <v>13.8156</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.06</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2044</v>
+        <v>0.2137</v>
       </c>
       <c r="J125" t="n">
-        <v>5.9276</v>
+        <v>6.1973</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.87</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4667</v>
+        <v>-0.4424</v>
       </c>
       <c r="J126" t="n">
-        <v>-13.5343</v>
+        <v>-12.8296</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.51</v>
       </c>
       <c r="I127" t="n">
-        <v>0.6865</v>
+        <v>0.769</v>
       </c>
       <c r="J127" t="n">
-        <v>19.9085</v>
+        <v>22.301</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.38</v>
       </c>
       <c r="I128" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.6303</v>
       </c>
       <c r="J128" t="n">
-        <v>16.327</v>
+        <v>18.2787</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.16</v>
       </c>
       <c r="I129" t="n">
-        <v>0.3379</v>
+        <v>0.3492</v>
       </c>
       <c r="J129" t="n">
-        <v>9.799099999999999</v>
+        <v>10.1268</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2381</v>
+        <v>-0.2496</v>
       </c>
       <c r="J130" t="n">
-        <v>-6.9049</v>
+        <v>-7.2384</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.55</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4821</v>
+        <v>-0.4864</v>
       </c>
       <c r="J131" t="n">
-        <v>-13.9809</v>
+        <v>-14.1056</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.55</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9341</v>
+        <v>1.0275</v>
       </c>
       <c r="J132" t="n">
-        <v>19.6161</v>
+        <v>21.5775</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.45</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8056</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="J133" t="n">
-        <v>16.9176</v>
+        <v>18.6816</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.07</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2173</v>
+        <v>0.2303</v>
       </c>
       <c r="J134" t="n">
-        <v>4.5633</v>
+        <v>4.8363</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.06</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1866</v>
+        <v>0.2014</v>
       </c>
       <c r="J135" t="n">
-        <v>3.9186</v>
+        <v>4.2294</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.82</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.6206</v>
+        <v>-0.5773</v>
       </c>
       <c r="J136" t="n">
-        <v>-13.0326</v>
+        <v>-12.1233</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.22</v>
       </c>
       <c r="I137" t="n">
-        <v>0.427</v>
+        <v>0.4689</v>
       </c>
       <c r="J137" t="n">
-        <v>8.967000000000001</v>
+        <v>9.8469</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.2</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4051</v>
+        <v>0.4417</v>
       </c>
       <c r="J138" t="n">
-        <v>8.507099999999999</v>
+        <v>9.275700000000001</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.08</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2169</v>
+        <v>0.2211</v>
       </c>
       <c r="J139" t="n">
-        <v>4.5549</v>
+        <v>4.6431</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.65</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.378</v>
+        <v>-0.3889</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.938</v>
+        <v>-8.1669</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.62</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4059</v>
+        <v>-0.4157</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.523899999999999</v>
+        <v>-8.729699999999999</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.96</v>
       </c>
       <c r="I142" t="n">
-        <v>1.3714</v>
+        <v>1.498</v>
       </c>
       <c r="J142" t="n">
-        <v>23.3138</v>
+        <v>25.466</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.49</v>
       </c>
       <c r="I143" t="n">
-        <v>0.8196</v>
+        <v>0.9122</v>
       </c>
       <c r="J143" t="n">
-        <v>13.9332</v>
+        <v>15.5074</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.31</v>
       </c>
       <c r="I144" t="n">
-        <v>0.597</v>
+        <v>0.6677</v>
       </c>
       <c r="J144" t="n">
-        <v>10.149</v>
+        <v>11.3509</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.26</v>
       </c>
       <c r="I145" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.5931</v>
       </c>
       <c r="J145" t="n">
-        <v>9.004899999999999</v>
+        <v>10.0827</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.93</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3573</v>
+        <v>-0.3276</v>
       </c>
       <c r="J146" t="n">
-        <v>-6.0741</v>
+        <v>-5.5692</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>0.93</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.0533</v>
+        <v>-0.0752</v>
       </c>
       <c r="J147" t="n">
-        <v>-0.9061</v>
+        <v>-1.2784</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.74</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.2621</v>
+        <v>-0.2826</v>
       </c>
       <c r="J148" t="n">
-        <v>-4.4557</v>
+        <v>-4.8042</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.3073</v>
+        <v>-0.327</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.2241</v>
+        <v>-5.559</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.63</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3628</v>
+        <v>-0.3804</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.1676</v>
+        <v>-6.4668</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4283</v>
+        <v>-0.4425</v>
       </c>
       <c r="J151" t="n">
-        <v>-7.2811</v>
+        <v>-7.5225</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7910/event_7910_evp_summary.xlsx
+++ b/database/event/7910/event_7910_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.269399999999999</v>
+        <v>8.498799999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>3.7724</v>
+        <v>3.8771</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1402</v>
+        <v>3.1824</v>
       </c>
       <c r="E2" t="n">
-        <v>8.269399999999999</v>
+        <v>8.498799999999999</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.5796</v>
+        <v>3.7063</v>
       </c>
       <c r="C3" t="n">
-        <v>1.633</v>
+        <v>1.6908</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0053</v>
+        <v>1.0417</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5796</v>
+        <v>3.7063</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.4926</v>
+        <v>3.6661</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5933</v>
+        <v>1.6724</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9657</v>
+        <v>1.0237</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4926</v>
+        <v>3.6661</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.2356</v>
+        <v>3.1843</v>
       </c>
       <c r="C5" t="n">
-        <v>1.476</v>
+        <v>1.4526</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8487</v>
+        <v>0.8085</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2356</v>
+        <v>3.1843</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.1342</v>
+        <v>3.0814</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4298</v>
+        <v>1.4057</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8025</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>3.1342</v>
+        <v>3.0814</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.9861</v>
+        <v>3.0797</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3622</v>
+        <v>1.4049</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7351</v>
+        <v>0.7618</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9861</v>
+        <v>3.0797</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9861</v>
+        <v>2.9866</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3473</v>
+        <v>2.3477</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>168</v>
       </c>
       <c r="M7" t="n">
-        <v>2.3473</v>
+        <v>2.3477</v>
       </c>
       <c r="N7" t="n">
         <v>168</v>
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.8439</v>
+        <v>2.7897</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2974</v>
+        <v>1.2726</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6704</v>
+        <v>0.6323</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8439</v>
+        <v>2.7897</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8439</v>
+        <v>2.8443</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2355</v>
+        <v>2.2358</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>168</v>
       </c>
       <c r="M8" t="n">
-        <v>2.2355</v>
+        <v>2.2358</v>
       </c>
       <c r="N8" t="n">
         <v>168</v>
@@ -814,26 +814,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.8576</v>
+        <v>2.1564</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8474</v>
+        <v>0.9837</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2214</v>
+        <v>0.3494</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8576</v>
+        <v>2.1564</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8576</v>
+        <v>1.7239</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -842,44 +842,44 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4602</v>
+        <v>1.3551</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>108</v>
+        <v>39</v>
       </c>
       <c r="M9" t="n">
-        <v>1.4602</v>
+        <v>1.3551</v>
       </c>
       <c r="N9" t="n">
-        <v>108</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.8012</v>
+        <v>2.008</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8217</v>
+        <v>0.916</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1957</v>
+        <v>0.2831</v>
       </c>
       <c r="E10" t="n">
-        <v>1.8012</v>
+        <v>2.008</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8012</v>
+        <v>1.8576</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -888,44 +888,44 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4159</v>
+        <v>1.4602</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="M10" t="n">
-        <v>1.4159</v>
+        <v>1.4602</v>
       </c>
       <c r="N10" t="n">
-        <v>86</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.7577</v>
+        <v>2.008</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8018</v>
+        <v>0.916</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1759</v>
+        <v>0.2831</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7577</v>
+        <v>2.008</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7577</v>
+        <v>1.8012</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -934,44 +934,44 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3817</v>
+        <v>1.4159</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="M11" t="n">
-        <v>1.3817</v>
+        <v>1.4159</v>
       </c>
       <c r="N11" t="n">
-        <v>108</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.7242</v>
+        <v>1.9001</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7866</v>
+        <v>0.8668</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1607</v>
+        <v>0.2349</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7242</v>
+        <v>1.9001</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1.7242</v>
+        <v>1.7577</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -980,44 +980,44 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3553</v>
+        <v>1.3817</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>39</v>
+        <v>108</v>
       </c>
       <c r="M12" t="n">
-        <v>1.3553</v>
+        <v>1.3817</v>
       </c>
       <c r="N12" t="n">
-        <v>39</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>jottAAA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.5908</v>
+        <v>1.8227</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7257</v>
+        <v>0.8315</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1</v>
+        <v>0.2003</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5908</v>
+        <v>1.8227</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.5908</v>
+        <v>1.577</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1026,44 +1026,44 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.2505</v>
+        <v>1.2396</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2505</v>
+        <v>1.2396</v>
       </c>
       <c r="N13" t="n">
-        <v>86</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>jottAAA</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.577</v>
+        <v>1.5661</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7194</v>
+        <v>0.7144</v>
       </c>
       <c r="D14" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.0857</v>
       </c>
       <c r="E14" t="n">
-        <v>1.577</v>
+        <v>1.5661</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.577</v>
+        <v>1.5309</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1072,44 +1072,44 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2396</v>
+        <v>1.2034</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>53</v>
+        <v>168</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2396</v>
+        <v>1.2034</v>
       </c>
       <c r="N14" t="n">
-        <v>53</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.5305</v>
+        <v>1.4648</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6982</v>
+        <v>0.6682</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0725</v>
+        <v>0.0405</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5305</v>
+        <v>1.4648</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5305</v>
+        <v>1.5735</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1118,44 +1118,44 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2031</v>
+        <v>1.2369</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>168</v>
+        <v>86</v>
       </c>
       <c r="M15" t="n">
-        <v>1.2031</v>
+        <v>1.2369</v>
       </c>
       <c r="N15" t="n">
-        <v>168</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.2711</v>
+        <v>1.4507</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5799</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0456</v>
+        <v>0.0342</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2711</v>
+        <v>1.4507</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2711</v>
+        <v>1.2416</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1164,44 +1164,44 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9992</v>
+        <v>0.976</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9992</v>
+        <v>0.976</v>
       </c>
       <c r="N16" t="n">
-        <v>108</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.2416</v>
+        <v>1.1326</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5664</v>
+        <v>0.5167</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.059</v>
+        <v>-0.1079</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2416</v>
+        <v>1.1326</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2416</v>
+        <v>1.2711</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1210,19 +1210,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.976</v>
+        <v>0.9992</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="M17" t="n">
-        <v>0.976</v>
+        <v>0.9992</v>
       </c>
       <c r="N17" t="n">
-        <v>53</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9619</v>
+        <v>0.8827</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4388</v>
+        <v>0.4027</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1863</v>
+        <v>-0.2195</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9619</v>
+        <v>0.8827</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9619</v>
+        <v>0.9623</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7561</v>
+        <v>0.7564</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>168</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7561</v>
+        <v>0.7564</v>
       </c>
       <c r="N18" t="n">
         <v>168</v>
@@ -1278,16 +1278,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7849</v>
+        <v>0.7966</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3581</v>
+        <v>0.3634</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2669</v>
+        <v>-0.258</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7849</v>
+        <v>0.7966</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1324,22 +1324,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6773</v>
+        <v>0.5524</v>
       </c>
       <c r="C20" t="n">
-        <v>0.309</v>
+        <v>0.252</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3159</v>
+        <v>-0.3671</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6773</v>
+        <v>0.5524</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6773</v>
+        <v>0.6767</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5324</v>
+        <v>0.5319</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>39</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5324</v>
+        <v>0.5319</v>
       </c>
       <c r="N20" t="n">
         <v>39</v>
@@ -1366,26 +1366,26 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.3717</v>
+        <v>0.4817</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1696</v>
+        <v>0.2197</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.455</v>
+        <v>-0.3987</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3717</v>
+        <v>0.4817</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3717</v>
+        <v>0.3309</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1394,44 +1394,44 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2922</v>
+        <v>0.2601</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>158</v>
+        <v>53</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2922</v>
+        <v>0.2601</v>
       </c>
       <c r="N21" t="n">
-        <v>158</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3309</v>
+        <v>0.4153</v>
       </c>
       <c r="C22" t="n">
-        <v>0.151</v>
+        <v>0.1895</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4736</v>
+        <v>-0.4283</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3309</v>
+        <v>0.4153</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3309</v>
+        <v>0.0336</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1440,44 +1440,44 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2601</v>
+        <v>0.0264</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2601</v>
+        <v>0.0264</v>
       </c>
       <c r="N22" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2926</v>
+        <v>0.3281</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1335</v>
+        <v>0.1497</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.491</v>
+        <v>-0.4673</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2926</v>
+        <v>0.3281</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2926</v>
+        <v>0.3717</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1486,44 +1486,44 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.23</v>
+        <v>0.2922</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>64</v>
+        <v>158</v>
       </c>
       <c r="M23" t="n">
-        <v>0.23</v>
+        <v>0.2922</v>
       </c>
       <c r="N23" t="n">
-        <v>64</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2083</v>
+        <v>0.265</v>
       </c>
       <c r="C24" t="n">
-        <v>0.095</v>
+        <v>0.1209</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5294</v>
+        <v>-0.4955</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2083</v>
+        <v>0.265</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2083</v>
+        <v>0.2926</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1532,7 +1532,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1637</v>
+        <v>0.23</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>64</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1637</v>
+        <v>0.23</v>
       </c>
       <c r="N24" t="n">
         <v>64</v>
@@ -1550,26 +1550,26 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.078</v>
+        <v>0.2327</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0356</v>
+        <v>0.1062</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5887</v>
+        <v>-0.5099</v>
       </c>
       <c r="E25" t="n">
-        <v>0.078</v>
+        <v>0.2327</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.078</v>
+        <v>0.0195</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1578,44 +1578,44 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0613</v>
+        <v>0.0153</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0613</v>
+        <v>0.0153</v>
       </c>
       <c r="N25" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0336</v>
+        <v>0.2308</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0153</v>
+        <v>0.1053</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6089</v>
+        <v>-0.5107</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0336</v>
+        <v>0.2308</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0336</v>
+        <v>0.2083</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1624,44 +1624,44 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0264</v>
+        <v>0.1637</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0264</v>
+        <v>0.1637</v>
       </c>
       <c r="N26" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0197</v>
+        <v>0.089</v>
       </c>
       <c r="C27" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0406</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6152</v>
+        <v>-0.5741000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0197</v>
+        <v>0.089</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0197</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1670,19 +1670,19 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0155</v>
+        <v>-0.0615</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0155</v>
+        <v>-0.0615</v>
       </c>
       <c r="N27" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28">
@@ -1692,22 +1692,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0447</v>
+        <v>-0.0465</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0204</v>
+        <v>-0.0212</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6446</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0447</v>
+        <v>-0.0465</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.0447</v>
+        <v>-0.0636</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1716,7 +1716,7 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.0351</v>
+        <v>-0.05</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>168</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0351</v>
+        <v>-0.05</v>
       </c>
       <c r="N28" t="n">
         <v>168</v>
@@ -1734,26 +1734,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.1533</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0357</v>
+        <v>-0.0699</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6598000000000001</v>
+        <v>-0.6823</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.1533</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.07820000000000001</v>
+        <v>0.078</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1762,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.0615</v>
+        <v>0.0613</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>38</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.0615</v>
+        <v>0.0613</v>
       </c>
       <c r="N29" t="n">
         <v>38</v>
@@ -1784,16 +1784,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3504</v>
+        <v>-0.4913</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1598</v>
+        <v>-0.2241</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7837</v>
+        <v>-0.8333</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.3504</v>
+        <v>-0.4913</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1826,26 +1826,26 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4388</v>
+        <v>-0.5644</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2002</v>
+        <v>-0.2575</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.824</v>
+        <v>-0.8659</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4388</v>
+        <v>-0.5644</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.4388</v>
+        <v>-0.5286</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1854,44 +1854,44 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.3449</v>
+        <v>-0.4155</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3449</v>
+        <v>-0.4155</v>
       </c>
       <c r="N31" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5286</v>
+        <v>-0.5793</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2411</v>
+        <v>-0.2643</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8648</v>
+        <v>-0.8726</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5286</v>
+        <v>-0.5793</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.5286</v>
+        <v>-0.5452</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1900,44 +1900,44 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.4155</v>
+        <v>-0.4286</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>64</v>
+        <v>108</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4155</v>
+        <v>-0.4286</v>
       </c>
       <c r="N32" t="n">
-        <v>64</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5341</v>
+        <v>-0.581</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2437</v>
+        <v>-0.265</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8673</v>
+        <v>-0.8733</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5341</v>
+        <v>-0.581</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.5341</v>
+        <v>-0.4388</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1946,44 +1946,44 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.4198</v>
+        <v>-0.3449</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4198</v>
+        <v>-0.3449</v>
       </c>
       <c r="N33" t="n">
-        <v>86</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5452</v>
+        <v>-0.6269</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2487</v>
+        <v>-0.286</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8724</v>
+        <v>-0.8938</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5452</v>
+        <v>-0.6269</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.5452</v>
+        <v>-0.5039</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1992,44 +1992,44 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.4286</v>
+        <v>-0.3961</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4286</v>
+        <v>-0.3961</v>
       </c>
       <c r="N34" t="n">
-        <v>108</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.5904</v>
+        <v>-0.7291</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2693</v>
+        <v>-0.3326</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.893</v>
+        <v>-0.9395</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5904</v>
+        <v>-0.7291</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.5904</v>
+        <v>-0.7228</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2038,44 +2038,44 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.4641</v>
+        <v>-0.5682</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.4641</v>
+        <v>-0.5682</v>
       </c>
       <c r="N35" t="n">
-        <v>38</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7228</v>
+        <v>-1.0058</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3297</v>
+        <v>-0.4588</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9532</v>
+        <v>-1.0631</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7228</v>
+        <v>-1.0058</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.7228</v>
+        <v>-0.9448</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2084,44 +2084,44 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.5682</v>
+        <v>-0.7427</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.5682</v>
+        <v>-0.7427</v>
       </c>
       <c r="N36" t="n">
-        <v>108</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9448</v>
+        <v>-1.0804</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.431</v>
+        <v>-0.4929</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0543</v>
+        <v>-1.0964</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9448</v>
+        <v>-1.0804</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.9448</v>
+        <v>-0.5904</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2130,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.7427</v>
+        <v>-0.4641</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>38</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7427</v>
+        <v>-0.4641</v>
       </c>
       <c r="N37" t="n">
         <v>38</v>
@@ -2152,22 +2152,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0054</v>
+        <v>-1.159</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4587</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0819</v>
+        <v>-1.1315</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0054</v>
+        <v>-1.159</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.0054</v>
+        <v>-1.0055</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.7903</v>
+        <v>-0.7904</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>39</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.7903</v>
+        <v>-0.7904</v>
       </c>
       <c r="N38" t="n">
         <v>39</v>
@@ -2194,26 +2194,26 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.1569</v>
+        <v>-1.3926</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.5278</v>
+        <v>-0.6353</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1508</v>
+        <v>-1.2359</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.1569</v>
+        <v>-1.3926</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.1569</v>
+        <v>-1.1681</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2222,44 +2222,44 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.9094</v>
+        <v>-0.9182</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.9094</v>
+        <v>-0.9182</v>
       </c>
       <c r="N39" t="n">
-        <v>39</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.1681</v>
+        <v>-1.4787</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5329</v>
+        <v>-0.6746</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1559</v>
+        <v>-1.2743</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.1681</v>
+        <v>-1.4787</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.1681</v>
+        <v>-1.1444</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2268,19 +2268,19 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.9182</v>
+        <v>-0.8996</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.9182</v>
+        <v>-0.8996</v>
       </c>
       <c r="N40" t="n">
-        <v>86</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41">
@@ -2290,16 +2290,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.2244</v>
+        <v>-1.5757</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5586</v>
+        <v>-0.7188</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1816</v>
+        <v>-1.3177</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.2244</v>
+        <v>-1.5757</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -5429,10 +5429,10 @@
         <v>1.56</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8246</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="J77" t="n">
-        <v>18.9658</v>
+        <v>18.9543</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.13</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2983</v>
+        <v>0.2981</v>
       </c>
       <c r="J78" t="n">
-        <v>6.8609</v>
+        <v>6.8563</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.13</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2983</v>
+        <v>0.2981</v>
       </c>
       <c r="J79" t="n">
-        <v>6.8609</v>
+        <v>6.8563</v>
       </c>
     </row>
     <row r="80">
@@ -5546,13 +5546,13 @@
         <v>23</v>
       </c>
       <c r="H80" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2582</v>
+        <v>-0.2484</v>
       </c>
       <c r="J80" t="n">
-        <v>-5.9386</v>
+        <v>-5.7132</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.71</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3441</v>
+        <v>-0.3442</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.9143</v>
+        <v>-7.9166</v>
       </c>
     </row>
     <row r="82">
@@ -6829,10 +6829,10 @@
         <v>1.59</v>
       </c>
       <c r="I112" t="n">
-        <v>1.0696</v>
+        <v>1.07</v>
       </c>
       <c r="J112" t="n">
-        <v>25.6704</v>
+        <v>25.68</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.34</v>
       </c>
       <c r="I113" t="n">
-        <v>0.7244</v>
+        <v>0.7247</v>
       </c>
       <c r="J113" t="n">
-        <v>17.3856</v>
+        <v>17.3928</v>
       </c>
     </row>
     <row r="114">
@@ -6906,13 +6906,13 @@
         <v>24</v>
       </c>
       <c r="H114" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="I114" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.5915</v>
       </c>
       <c r="J114" t="n">
-        <v>14.5536</v>
+        <v>14.196</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.14</v>
       </c>
       <c r="I115" t="n">
-        <v>0.4036</v>
+        <v>0.4039</v>
       </c>
       <c r="J115" t="n">
-        <v>9.686400000000001</v>
+        <v>9.6936</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.87</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4645</v>
+        <v>-0.4642</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.148</v>
+        <v>-11.1408</v>
       </c>
     </row>
     <row r="117">
@@ -7626,13 +7626,13 @@
         <v>21</v>
       </c>
       <c r="H132" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0275</v>
+        <v>1.0139</v>
       </c>
       <c r="J132" t="n">
-        <v>21.5775</v>
+        <v>21.2919</v>
       </c>
     </row>
     <row r="133">
@@ -7786,13 +7786,13 @@
         <v>21</v>
       </c>
       <c r="H136" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5773</v>
+        <v>-0.5536</v>
       </c>
       <c r="J136" t="n">
-        <v>-12.1233</v>
+        <v>-11.6256</v>
       </c>
     </row>
     <row r="137">

--- a/database/event/7910/event_7910_evp_summary.xlsx
+++ b/database/event/7910/event_7910_evp_summary.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.498799999999999</v>
+        <v>8.5318</v>
       </c>
       <c r="C2" t="n">
-        <v>3.8771</v>
+        <v>3.8921</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1824</v>
+        <v>3.2809</v>
       </c>
       <c r="E2" t="n">
-        <v>8.498799999999999</v>
+        <v>8.5318</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>8.269399999999999</v>
+        <v>8.3024</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>6.5003</v>
+        <v>6.564</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>158</v>
       </c>
       <c r="M2" t="n">
-        <v>6.5003</v>
+        <v>6.564</v>
       </c>
       <c r="N2" t="n">
         <v>158</v>
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.7063</v>
+        <v>3.5818</v>
       </c>
       <c r="C3" t="n">
-        <v>1.6908</v>
+        <v>1.634</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0417</v>
+        <v>1.0259</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7063</v>
+        <v>3.5818</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5796</v>
+        <v>3.4551</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8138</v>
+        <v>2.7317</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>158</v>
       </c>
       <c r="M3" t="n">
-        <v>2.8138</v>
+        <v>2.7317</v>
       </c>
       <c r="N3" t="n">
         <v>158</v>
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.6661</v>
+        <v>3.5018</v>
       </c>
       <c r="C4" t="n">
-        <v>1.6724</v>
+        <v>1.5975</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0237</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6661</v>
+        <v>3.5018</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4926</v>
+        <v>3.3283</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7454</v>
+        <v>2.6314</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>86</v>
       </c>
       <c r="M4" t="n">
-        <v>2.7454</v>
+        <v>2.6314</v>
       </c>
       <c r="N4" t="n">
         <v>86</v>
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.1843</v>
+        <v>3.1102</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4526</v>
+        <v>1.4188</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8085</v>
+        <v>0.8111</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1843</v>
+        <v>3.1102</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2356</v>
+        <v>3.1615</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5434</v>
+        <v>2.4996</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>158</v>
       </c>
       <c r="M5" t="n">
-        <v>2.5434</v>
+        <v>2.4996</v>
       </c>
       <c r="N5" t="n">
         <v>158</v>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.0814</v>
+        <v>3.0621</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4057</v>
+        <v>1.3969</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7625999999999999</v>
+        <v>0.7891</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0814</v>
+        <v>3.0621</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1342</v>
+        <v>3.1149</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.4637</v>
+        <v>2.4627</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>158</v>
       </c>
       <c r="M6" t="n">
-        <v>2.4637</v>
+        <v>2.4627</v>
       </c>
       <c r="N6" t="n">
         <v>158</v>
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.0797</v>
+        <v>3.0423</v>
       </c>
       <c r="C7" t="n">
-        <v>1.4049</v>
+        <v>1.3879</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7618</v>
+        <v>0.7801</v>
       </c>
       <c r="E7" t="n">
-        <v>3.0797</v>
+        <v>3.0423</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9866</v>
+        <v>2.9492</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3477</v>
+        <v>2.3317</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>168</v>
       </c>
       <c r="M7" t="n">
-        <v>2.3477</v>
+        <v>2.3317</v>
       </c>
       <c r="N7" t="n">
         <v>168</v>
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.7897</v>
+        <v>2.6391</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2726</v>
+        <v>1.2039</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6323</v>
+        <v>0.5964</v>
       </c>
       <c r="E8" t="n">
-        <v>2.7897</v>
+        <v>2.6391</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8443</v>
+        <v>2.6937</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2358</v>
+        <v>2.1297</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>168</v>
       </c>
       <c r="M8" t="n">
-        <v>2.2358</v>
+        <v>2.1297</v>
       </c>
       <c r="N8" t="n">
         <v>168</v>
@@ -818,22 +818,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.1564</v>
+        <v>2.0676</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9837</v>
+        <v>0.9432</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3494</v>
+        <v>0.3361</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1564</v>
+        <v>2.0676</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.7239</v>
+        <v>1.6351</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3551</v>
+        <v>1.2927</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>39</v>
       </c>
       <c r="M9" t="n">
-        <v>1.3551</v>
+        <v>1.2927</v>
       </c>
       <c r="N9" t="n">
         <v>39</v>
@@ -860,26 +860,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.008</v>
+        <v>2.0254</v>
       </c>
       <c r="C10" t="n">
-        <v>0.916</v>
+        <v>0.924</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2831</v>
+        <v>0.3169</v>
       </c>
       <c r="E10" t="n">
-        <v>2.008</v>
+        <v>2.0254</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8576</v>
+        <v>1.8186</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -888,44 +888,44 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4602</v>
+        <v>1.4378</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="M10" t="n">
-        <v>1.4602</v>
+        <v>1.4378</v>
       </c>
       <c r="N10" t="n">
-        <v>108</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.008</v>
+        <v>1.9487</v>
       </c>
       <c r="C11" t="n">
-        <v>0.916</v>
+        <v>0.889</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2831</v>
+        <v>0.2819</v>
       </c>
       <c r="E11" t="n">
-        <v>2.008</v>
+        <v>1.9487</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8012</v>
+        <v>1.7983</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -934,19 +934,19 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4159</v>
+        <v>1.4218</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="M11" t="n">
-        <v>1.4159</v>
+        <v>1.4218</v>
       </c>
       <c r="N11" t="n">
-        <v>86</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12">
@@ -956,22 +956,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.9001</v>
+        <v>1.7718</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8668</v>
+        <v>0.8083</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2349</v>
+        <v>0.2014</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9001</v>
+        <v>1.7718</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1.7577</v>
+        <v>1.6294</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3817</v>
+        <v>1.2882</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>108</v>
       </c>
       <c r="M12" t="n">
-        <v>1.3817</v>
+        <v>1.2882</v>
       </c>
       <c r="N12" t="n">
         <v>108</v>
@@ -1002,22 +1002,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.8227</v>
+        <v>1.6987</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8315</v>
+        <v>0.7749</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2003</v>
+        <v>0.1681</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8227</v>
+        <v>1.6987</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.577</v>
+        <v>1.453</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.2396</v>
+        <v>1.1488</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>53</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2396</v>
+        <v>1.1488</v>
       </c>
       <c r="N13" t="n">
         <v>53</v>
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.5661</v>
+        <v>1.4986</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7144</v>
+        <v>0.6836</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0857</v>
+        <v>0.0769</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5661</v>
+        <v>1.4986</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5309</v>
+        <v>1.4634</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2034</v>
+        <v>1.157</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>168</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2034</v>
+        <v>1.157</v>
       </c>
       <c r="N14" t="n">
         <v>168</v>
@@ -1094,22 +1094,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.4648</v>
+        <v>1.4821</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6682</v>
+        <v>0.6761</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0405</v>
+        <v>0.0694</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4648</v>
+        <v>1.4821</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5735</v>
+        <v>1.5908</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2369</v>
+        <v>1.2577</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>86</v>
       </c>
       <c r="M15" t="n">
-        <v>1.2369</v>
+        <v>1.2577</v>
       </c>
       <c r="N15" t="n">
         <v>86</v>
@@ -1140,22 +1140,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4507</v>
+        <v>1.3348</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.6089</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0342</v>
+        <v>0.0023</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4507</v>
+        <v>1.3348</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2416</v>
+        <v>1.1257</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.976</v>
+        <v>0.89</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>53</v>
       </c>
       <c r="M16" t="n">
-        <v>0.976</v>
+        <v>0.89</v>
       </c>
       <c r="N16" t="n">
         <v>53</v>
@@ -1186,22 +1186,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.1326</v>
+        <v>1.0328</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5167</v>
+        <v>0.4712</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1079</v>
+        <v>-0.1353</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1326</v>
+        <v>1.0328</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2711</v>
+        <v>1.1713</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9992</v>
+        <v>0.9261</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>108</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9992</v>
+        <v>0.9261</v>
       </c>
       <c r="N17" t="n">
         <v>108</v>
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8827</v>
+        <v>0.7571</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4027</v>
+        <v>0.3454</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2195</v>
+        <v>-0.2609</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8827</v>
+        <v>0.7571</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9623</v>
+        <v>0.8367</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7564</v>
+        <v>0.6615</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>168</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7564</v>
+        <v>0.6615</v>
       </c>
       <c r="N18" t="n">
         <v>168</v>
@@ -1278,22 +1278,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7966</v>
+        <v>0.7274</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3634</v>
+        <v>0.3318</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.258</v>
+        <v>-0.2744</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7966</v>
+        <v>0.7274</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7849</v>
+        <v>0.7157</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.617</v>
+        <v>0.5659</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>64</v>
       </c>
       <c r="M19" t="n">
-        <v>0.617</v>
+        <v>0.5659</v>
       </c>
       <c r="N19" t="n">
         <v>64</v>
@@ -1324,22 +1324,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5524</v>
+        <v>0.5192</v>
       </c>
       <c r="C20" t="n">
-        <v>0.252</v>
+        <v>0.2369</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3671</v>
+        <v>-0.3693</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5524</v>
+        <v>0.5192</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6767</v>
+        <v>0.6435</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5319</v>
+        <v>0.5088</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>39</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5319</v>
+        <v>0.5088</v>
       </c>
       <c r="N20" t="n">
         <v>39</v>
@@ -1370,22 +1370,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4817</v>
+        <v>0.456</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2197</v>
+        <v>0.208</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3987</v>
+        <v>-0.3981</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4817</v>
+        <v>0.456</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3309</v>
+        <v>0.3052</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2601</v>
+        <v>0.2413</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>53</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2601</v>
+        <v>0.2413</v>
       </c>
       <c r="N21" t="n">
         <v>53</v>
@@ -1416,22 +1416,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4153</v>
+        <v>0.3653</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1895</v>
+        <v>0.1666</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4283</v>
+        <v>-0.4394</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4153</v>
+        <v>0.3653</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0336</v>
+        <v>-0.0164</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0264</v>
+        <v>-0.013</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>38</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0264</v>
+        <v>-0.013</v>
       </c>
       <c r="N22" t="n">
         <v>38</v>
@@ -1462,22 +1462,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3281</v>
+        <v>0.2872</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1497</v>
+        <v>0.131</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4673</v>
+        <v>-0.475</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3281</v>
+        <v>0.2872</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3717</v>
+        <v>0.3308</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1486,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2922</v>
+        <v>0.2615</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>158</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2922</v>
+        <v>0.2615</v>
       </c>
       <c r="N23" t="n">
         <v>158</v>
@@ -1504,26 +1504,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.265</v>
+        <v>0.193</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1209</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4955</v>
+        <v>-0.5179</v>
       </c>
       <c r="E24" t="n">
-        <v>0.265</v>
+        <v>0.193</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2926</v>
+        <v>-0.0202</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1532,44 +1532,44 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.23</v>
+        <v>-0.016</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="M24" t="n">
-        <v>0.23</v>
+        <v>-0.016</v>
       </c>
       <c r="N24" t="n">
-        <v>64</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2327</v>
+        <v>0.1895</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1062</v>
+        <v>0.0864</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5099</v>
+        <v>-0.5195</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2327</v>
+        <v>0.1895</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0195</v>
+        <v>0.2171</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1578,19 +1578,19 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0153</v>
+        <v>0.1716</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0153</v>
+        <v>0.1716</v>
       </c>
       <c r="N25" t="n">
-        <v>39</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26">
@@ -1600,22 +1600,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2308</v>
+        <v>0.1886</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1053</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5107</v>
+        <v>-0.5199</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2308</v>
+        <v>0.1886</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2083</v>
+        <v>0.1661</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1624,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1637</v>
+        <v>0.1313</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>64</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1637</v>
+        <v>0.1313</v>
       </c>
       <c r="N26" t="n">
         <v>64</v>
@@ -1646,22 +1646,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.089</v>
+        <v>0.052</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0406</v>
+        <v>0.0237</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5741000000000001</v>
+        <v>-0.5821</v>
       </c>
       <c r="E27" t="n">
-        <v>0.089</v>
+        <v>0.052</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.1152</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1670,7 +1670,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.0615</v>
+        <v>-0.0911</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>38</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0615</v>
+        <v>-0.0911</v>
       </c>
       <c r="N27" t="n">
         <v>38</v>
@@ -1692,22 +1692,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0465</v>
+        <v>-0.0958</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0212</v>
+        <v>-0.0437</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-0.6494</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0465</v>
+        <v>-0.0958</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.0636</v>
+        <v>-0.1129</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1716,7 +1716,7 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.05</v>
+        <v>-0.0893</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>168</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.05</v>
+        <v>-0.0893</v>
       </c>
       <c r="N28" t="n">
         <v>168</v>
@@ -1738,22 +1738,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1533</v>
+        <v>-0.2062</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0699</v>
+        <v>-0.0941</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6823</v>
+        <v>-0.6997</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1533</v>
+        <v>-0.2062</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.078</v>
+        <v>0.0251</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1762,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0613</v>
+        <v>0.0199</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>38</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0613</v>
+        <v>0.0199</v>
       </c>
       <c r="N29" t="n">
         <v>38</v>
@@ -1780,26 +1780,26 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4913</v>
+        <v>-0.5113</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2241</v>
+        <v>-0.2332</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.8333</v>
+        <v>-0.8387</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4913</v>
+        <v>-0.5113</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.3504</v>
+        <v>-0.4755</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1808,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.2754</v>
+        <v>-0.3759</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>64</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2754</v>
+        <v>-0.3759</v>
       </c>
       <c r="N30" t="n">
         <v>64</v>
@@ -1826,26 +1826,26 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.5644</v>
+        <v>-0.534</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2575</v>
+        <v>-0.2436</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8659</v>
+        <v>-0.8491</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5644</v>
+        <v>-0.534</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.5286</v>
+        <v>-0.3918</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1854,44 +1854,44 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.4155</v>
+        <v>-0.3098</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4155</v>
+        <v>-0.3098</v>
       </c>
       <c r="N31" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5793</v>
+        <v>-0.536</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2643</v>
+        <v>-0.2445</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8726</v>
+        <v>-0.85</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5793</v>
+        <v>-0.536</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.5452</v>
+        <v>-0.3951</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1900,44 +1900,44 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.4286</v>
+        <v>-0.3124</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>108</v>
+        <v>64</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4286</v>
+        <v>-0.3124</v>
       </c>
       <c r="N32" t="n">
-        <v>108</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.581</v>
+        <v>-0.5476</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.265</v>
+        <v>-0.2498</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8733</v>
+        <v>-0.8552</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.581</v>
+        <v>-0.5476</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.4388</v>
+        <v>-0.4246</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1946,44 +1946,44 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.3449</v>
+        <v>-0.3357</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3449</v>
+        <v>-0.3357</v>
       </c>
       <c r="N33" t="n">
-        <v>53</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6269</v>
+        <v>-0.6201</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.286</v>
+        <v>-0.2829</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8938</v>
+        <v>-0.8883</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6269</v>
+        <v>-0.6201</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.5039</v>
+        <v>-0.586</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1992,19 +1992,19 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.3961</v>
+        <v>-0.4633</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.3961</v>
+        <v>-0.4633</v>
       </c>
       <c r="N34" t="n">
-        <v>86</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35">
@@ -2014,22 +2014,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7291</v>
+        <v>-0.6359</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3326</v>
+        <v>-0.2901</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9395</v>
+        <v>-0.8955</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7291</v>
+        <v>-0.6359</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.7228</v>
+        <v>-0.6296</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.5682</v>
+        <v>-0.4978</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>108</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.5682</v>
+        <v>-0.4978</v>
       </c>
       <c r="N35" t="n">
         <v>108</v>
@@ -2060,22 +2060,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.0058</v>
+        <v>-0.9712</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.4588</v>
+        <v>-0.4431</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0631</v>
+        <v>-1.0482</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.0058</v>
+        <v>-0.9712</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.9448</v>
+        <v>-0.9102</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.7427</v>
+        <v>-0.7196</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>38</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7427</v>
+        <v>-0.7196</v>
       </c>
       <c r="N36" t="n">
         <v>38</v>
@@ -2106,22 +2106,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.0804</v>
+        <v>-1.0431</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4929</v>
+        <v>-0.4759</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0964</v>
+        <v>-1.081</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.0804</v>
+        <v>-1.0431</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.5904</v>
+        <v>-0.5531</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2130,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.4641</v>
+        <v>-0.4373</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>38</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.4641</v>
+        <v>-0.4373</v>
       </c>
       <c r="N37" t="n">
         <v>38</v>
@@ -2152,22 +2152,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.159</v>
+        <v>-1.126</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-0.5137</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1315</v>
+        <v>-1.1187</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.159</v>
+        <v>-1.126</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.0055</v>
+        <v>-0.9725</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.7904</v>
+        <v>-0.7689</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>39</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.7904</v>
+        <v>-0.7689</v>
       </c>
       <c r="N38" t="n">
         <v>39</v>
@@ -2198,22 +2198,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.3926</v>
+        <v>-1.3534</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.6353</v>
+        <v>-0.6173999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2359</v>
+        <v>-1.2223</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.3926</v>
+        <v>-1.3534</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.1681</v>
+        <v>-1.1289</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.9182</v>
+        <v>-0.8925</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>86</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.9182</v>
+        <v>-0.8925</v>
       </c>
       <c r="N39" t="n">
         <v>86</v>
@@ -2244,22 +2244,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.4787</v>
+        <v>-1.4776</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.6746</v>
+        <v>-0.6741</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2743</v>
+        <v>-1.2789</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.4787</v>
+        <v>-1.4776</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.1444</v>
+        <v>-1.1433</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.8996</v>
+        <v>-0.9039</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>39</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.8996</v>
+        <v>-0.9039</v>
       </c>
       <c r="N40" t="n">
         <v>39</v>
@@ -2290,22 +2290,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.5757</v>
+        <v>-1.5671</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.7188</v>
+        <v>-0.7149</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3177</v>
+        <v>-1.3197</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.5757</v>
+        <v>-1.5671</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.2244</v>
+        <v>-1.2158</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.9625</v>
+        <v>-0.9612000000000001</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>53</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.9625</v>
+        <v>-0.9612000000000001</v>
       </c>
       <c r="N41" t="n">
         <v>53</v>
@@ -2429,10 +2429,10 @@
         <v>1.34</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8474</v>
+        <v>0.8249</v>
       </c>
       <c r="J2" t="n">
-        <v>20.3376</v>
+        <v>19.7976</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5531</v>
+        <v>0.516</v>
       </c>
       <c r="J3" t="n">
-        <v>13.2744</v>
+        <v>12.384</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.13</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3939</v>
+        <v>0.3569</v>
       </c>
       <c r="J4" t="n">
-        <v>9.4536</v>
+        <v>8.5656</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.06</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2098</v>
+        <v>0.1803</v>
       </c>
       <c r="J5" t="n">
-        <v>5.0352</v>
+        <v>4.3272</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.97</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1607</v>
+        <v>-0.1292</v>
       </c>
       <c r="J6" t="n">
-        <v>-3.8568</v>
+        <v>-3.1008</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.13</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3344</v>
+        <v>0.2826</v>
       </c>
       <c r="J7" t="n">
-        <v>8.025600000000001</v>
+        <v>6.7824</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1437</v>
+        <v>0.1097</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4488</v>
+        <v>2.6328</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.02</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.0658</v>
       </c>
       <c r="J9" t="n">
-        <v>2.1792</v>
+        <v>1.5792</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.68</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3564</v>
+        <v>-0.3416</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.553599999999999</v>
+        <v>-8.198399999999999</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.62</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4104</v>
+        <v>-0.4003</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.849600000000001</v>
+        <v>-9.607200000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.42</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0001</v>
+        <v>0.9918</v>
       </c>
       <c r="J12" t="n">
-        <v>29.0029</v>
+        <v>28.7622</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.18</v>
       </c>
       <c r="I13" t="n">
-        <v>0.506</v>
+        <v>0.4693</v>
       </c>
       <c r="J13" t="n">
-        <v>14.674</v>
+        <v>13.6097</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.1</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3169</v>
+        <v>0.2827</v>
       </c>
       <c r="J14" t="n">
-        <v>9.190099999999999</v>
+        <v>8.1983</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.09</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2906</v>
+        <v>0.2574</v>
       </c>
       <c r="J15" t="n">
-        <v>8.4274</v>
+        <v>7.4646</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0261</v>
+        <v>-0.0206</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.7569</v>
+        <v>-0.5974</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.07</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1968</v>
+        <v>0.1558</v>
       </c>
       <c r="J17" t="n">
-        <v>5.7072</v>
+        <v>4.5182</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.06</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1751</v>
+        <v>0.1368</v>
       </c>
       <c r="J18" t="n">
-        <v>5.0779</v>
+        <v>3.9672</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.02</v>
       </c>
       <c r="I19" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0549</v>
       </c>
       <c r="J19" t="n">
-        <v>2.2417</v>
+        <v>1.5921</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0.003</v>
+        <v>0.0015</v>
       </c>
       <c r="J20" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0435</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.7</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.345</v>
+        <v>-0.3297</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.005</v>
+        <v>-9.561299999999999</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>2.53</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8453</v>
+        <v>1.9822</v>
       </c>
       <c r="J22" t="n">
-        <v>33.2154</v>
+        <v>35.6796</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.25</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6244</v>
+        <v>0.6002999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>11.2392</v>
+        <v>10.8054</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.2</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5167</v>
+        <v>0.4881</v>
       </c>
       <c r="J24" t="n">
-        <v>9.300599999999999</v>
+        <v>8.7858</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.05</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1361</v>
+        <v>0.1085</v>
       </c>
       <c r="J25" t="n">
-        <v>2.4498</v>
+        <v>1.953</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0669</v>
+        <v>-0.0646</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.2042</v>
+        <v>-1.1628</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>0.91</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.113</v>
+        <v>-0.0984</v>
       </c>
       <c r="J27" t="n">
-        <v>-2.034</v>
+        <v>-1.7712</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.87</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1594</v>
+        <v>-0.1437</v>
       </c>
       <c r="J28" t="n">
-        <v>-2.8692</v>
+        <v>-2.5866</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.77</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2602</v>
+        <v>-0.2436</v>
       </c>
       <c r="J29" t="n">
-        <v>-4.6836</v>
+        <v>-4.3848</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.72</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3061</v>
+        <v>-0.2899</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.5098</v>
+        <v>-5.2182</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.59</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4236</v>
+        <v>-0.4141</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.6248</v>
+        <v>-7.4538</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.43</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6999</v>
+        <v>0.6673</v>
       </c>
       <c r="J32" t="n">
-        <v>13.998</v>
+        <v>13.346</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.13</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3073</v>
+        <v>0.2563</v>
       </c>
       <c r="J33" t="n">
-        <v>6.146</v>
+        <v>5.126</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.03</v>
       </c>
       <c r="I34" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.0731</v>
       </c>
       <c r="J34" t="n">
-        <v>1.972</v>
+        <v>1.462</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.87</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1813</v>
+        <v>-0.1607</v>
       </c>
       <c r="J35" t="n">
-        <v>-3.626</v>
+        <v>-3.214</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.6</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4382</v>
+        <v>-0.4322</v>
       </c>
       <c r="J36" t="n">
-        <v>-8.763999999999999</v>
+        <v>-8.644</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.47</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9197</v>
+        <v>0.905</v>
       </c>
       <c r="J37" t="n">
-        <v>18.394</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.3</v>
       </c>
       <c r="I38" t="n">
-        <v>0.674</v>
+        <v>0.6604</v>
       </c>
       <c r="J38" t="n">
-        <v>13.48</v>
+        <v>13.208</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.22</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5507</v>
+        <v>0.5426</v>
       </c>
       <c r="J39" t="n">
-        <v>11.014</v>
+        <v>10.852</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.17</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4705</v>
+        <v>0.4462</v>
       </c>
       <c r="J40" t="n">
-        <v>9.41</v>
+        <v>8.923999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.74</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.756</v>
+        <v>-0.7311</v>
       </c>
       <c r="J41" t="n">
-        <v>-15.12</v>
+        <v>-14.622</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.15</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3697</v>
+        <v>0.3161</v>
       </c>
       <c r="J42" t="n">
-        <v>8.8728</v>
+        <v>7.5864</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.02</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0891</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="J43" t="n">
-        <v>2.1384</v>
+        <v>1.5408</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.96</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.0544</v>
       </c>
       <c r="J44" t="n">
-        <v>-1.5864</v>
+        <v>-1.3056</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.9</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1396</v>
+        <v>-0.1219</v>
       </c>
       <c r="J45" t="n">
-        <v>-3.3504</v>
+        <v>-2.9256</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.5</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.5181</v>
       </c>
       <c r="J46" t="n">
-        <v>-12.3744</v>
+        <v>-12.4344</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.47</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9139</v>
+        <v>0.8991</v>
       </c>
       <c r="J47" t="n">
-        <v>21.9336</v>
+        <v>21.5784</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.37</v>
       </c>
       <c r="I48" t="n">
-        <v>0.7726</v>
+        <v>0.7574</v>
       </c>
       <c r="J48" t="n">
-        <v>18.5424</v>
+        <v>18.1776</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.27</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6248</v>
+        <v>0.614</v>
       </c>
       <c r="J49" t="n">
-        <v>14.9952</v>
+        <v>14.736</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.05</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1681</v>
+        <v>0.142</v>
       </c>
       <c r="J50" t="n">
-        <v>4.0344</v>
+        <v>3.408</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.88</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4337</v>
+        <v>-0.3931</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.4088</v>
+        <v>-9.4344</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.21</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4603</v>
+        <v>0.4113</v>
       </c>
       <c r="J52" t="n">
-        <v>13.809</v>
+        <v>12.339</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.93</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1068</v>
+        <v>-0.0906</v>
       </c>
       <c r="J53" t="n">
-        <v>-3.204</v>
+        <v>-2.718</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.92</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1186</v>
+        <v>-0.1015</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.558</v>
+        <v>-3.045</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.86</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.185</v>
+        <v>-0.165</v>
       </c>
       <c r="J55" t="n">
-        <v>-5.55</v>
+        <v>-4.95</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.75</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2947</v>
+        <v>-0.2764</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.840999999999999</v>
+        <v>-8.292</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.37</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7836</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="J57" t="n">
-        <v>23.508</v>
+        <v>23.028</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.34</v>
       </c>
       <c r="I58" t="n">
-        <v>0.7393</v>
+        <v>0.7237</v>
       </c>
       <c r="J58" t="n">
-        <v>22.179</v>
+        <v>21.711</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.11</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3439</v>
+        <v>0.3085</v>
       </c>
       <c r="J59" t="n">
-        <v>10.317</v>
+        <v>9.255000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.04</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1468</v>
+        <v>0.1223</v>
       </c>
       <c r="J60" t="n">
-        <v>4.404</v>
+        <v>3.669</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.88</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.423</v>
+        <v>-0.381</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.69</v>
+        <v>-11.43</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.2</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4833</v>
+        <v>0.4508</v>
       </c>
       <c r="J62" t="n">
-        <v>8.699400000000001</v>
+        <v>8.1144</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.85</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.1851</v>
+        <v>-0.1684</v>
       </c>
       <c r="J63" t="n">
-        <v>-3.3318</v>
+        <v>-3.0312</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.83</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2056</v>
+        <v>-0.1885</v>
       </c>
       <c r="J64" t="n">
-        <v>-3.7008</v>
+        <v>-3.393</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.63</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3916</v>
+        <v>-0.3794</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.0488</v>
+        <v>-6.8292</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.51</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4973</v>
+        <v>-0.4962</v>
       </c>
       <c r="J66" t="n">
-        <v>-8.9514</v>
+        <v>-8.9316</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>2.44</v>
       </c>
       <c r="I67" t="n">
-        <v>2.0481</v>
+        <v>2.1383</v>
       </c>
       <c r="J67" t="n">
-        <v>36.8658</v>
+        <v>38.4894</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.59</v>
       </c>
       <c r="I68" t="n">
-        <v>1.041</v>
+        <v>1.0314</v>
       </c>
       <c r="J68" t="n">
-        <v>18.738</v>
+        <v>18.5652</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.05</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1373</v>
+        <v>0.1098</v>
       </c>
       <c r="J69" t="n">
-        <v>2.4714</v>
+        <v>1.9764</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.97</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2035</v>
+        <v>-0.1762</v>
       </c>
       <c r="J70" t="n">
-        <v>-3.663</v>
+        <v>-3.1716</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2995</v>
+        <v>-0.2661</v>
       </c>
       <c r="J71" t="n">
-        <v>-5.391</v>
+        <v>-4.7898</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.51</v>
       </c>
       <c r="I72" t="n">
-        <v>1.0023</v>
+        <v>0.9923</v>
       </c>
       <c r="J72" t="n">
-        <v>23.0529</v>
+        <v>22.8229</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.38</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8143</v>
+        <v>0.7985</v>
       </c>
       <c r="J73" t="n">
-        <v>18.7289</v>
+        <v>18.3655</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.02</v>
       </c>
       <c r="I74" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.0703</v>
       </c>
       <c r="J74" t="n">
-        <v>2.0447</v>
+        <v>1.6169</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.88</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4097</v>
+        <v>-0.3667</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.4231</v>
+        <v>-8.434100000000001</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.6</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.0314</v>
+        <v>-1.0338</v>
       </c>
       <c r="J76" t="n">
-        <v>-23.7222</v>
+        <v>-23.7774</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.56</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8241000000000001</v>
+        <v>0.7869</v>
       </c>
       <c r="J77" t="n">
-        <v>18.9543</v>
+        <v>18.0987</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.13</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2981</v>
+        <v>0.249</v>
       </c>
       <c r="J78" t="n">
-        <v>6.8563</v>
+        <v>5.727</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.13</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2981</v>
+        <v>0.249</v>
       </c>
       <c r="J79" t="n">
-        <v>6.8563</v>
+        <v>5.727</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2484</v>
+        <v>-0.2287</v>
       </c>
       <c r="J80" t="n">
-        <v>-5.7132</v>
+        <v>-5.2601</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.71</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3442</v>
+        <v>-0.3298</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.9166</v>
+        <v>-7.5854</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>2.12</v>
       </c>
       <c r="I82" t="n">
-        <v>1.6888</v>
+        <v>1.7284</v>
       </c>
       <c r="J82" t="n">
-        <v>27.0208</v>
+        <v>27.6544</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.93</v>
       </c>
       <c r="I83" t="n">
-        <v>1.4645</v>
+        <v>1.48</v>
       </c>
       <c r="J83" t="n">
-        <v>23.432</v>
+        <v>23.68</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.14</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3819</v>
+        <v>0.3501</v>
       </c>
       <c r="J84" t="n">
-        <v>6.1104</v>
+        <v>5.6016</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.92</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3545</v>
+        <v>-0.319</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.672</v>
+        <v>-5.104</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.79</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6751</v>
+        <v>-0.6498</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.8016</v>
+        <v>-10.3968</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.69</v>
       </c>
       <c r="I87" t="n">
-        <v>1.057</v>
+        <v>1.0527</v>
       </c>
       <c r="J87" t="n">
-        <v>16.912</v>
+        <v>16.8432</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.75</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2828</v>
+        <v>-0.265</v>
       </c>
       <c r="J88" t="n">
-        <v>-4.5248</v>
+        <v>-4.24</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.74</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2922</v>
+        <v>-0.2746</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.6752</v>
+        <v>-4.3936</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.57</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4462</v>
+        <v>-0.4391</v>
       </c>
       <c r="J90" t="n">
-        <v>-7.1392</v>
+        <v>-7.0256</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.33</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6512</v>
+        <v>-0.6752</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.4192</v>
+        <v>-10.8032</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.31</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6951000000000001</v>
+        <v>0.6802</v>
       </c>
       <c r="J92" t="n">
-        <v>20.1579</v>
+        <v>19.7258</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.3</v>
       </c>
       <c r="I93" t="n">
-        <v>0.68</v>
+        <v>0.6654</v>
       </c>
       <c r="J93" t="n">
-        <v>19.72</v>
+        <v>19.2966</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.13</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3935</v>
+        <v>0.3567</v>
       </c>
       <c r="J94" t="n">
-        <v>11.4115</v>
+        <v>10.3443</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.05</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1791</v>
+        <v>0.1519</v>
       </c>
       <c r="J95" t="n">
-        <v>5.1939</v>
+        <v>4.4051</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.93</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.287</v>
+        <v>-0.2469</v>
       </c>
       <c r="J96" t="n">
-        <v>-8.323</v>
+        <v>-7.1601</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.28</v>
       </c>
       <c r="I97" t="n">
-        <v>0.5429</v>
+        <v>0.517</v>
       </c>
       <c r="J97" t="n">
-        <v>15.7441</v>
+        <v>14.993</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.08</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2215</v>
+        <v>0.1776</v>
       </c>
       <c r="J98" t="n">
-        <v>6.4235</v>
+        <v>5.1504</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.05</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1559</v>
+        <v>0.12</v>
       </c>
       <c r="J99" t="n">
-        <v>4.5211</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.79</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2578</v>
+        <v>-0.2381</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.4762</v>
+        <v>-6.9049</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.468</v>
+        <v>-0.4648</v>
       </c>
       <c r="J101" t="n">
-        <v>-13.572</v>
+        <v>-13.4792</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.39</v>
       </c>
       <c r="I102" t="n">
-        <v>0.8212</v>
+        <v>0.8052</v>
       </c>
       <c r="J102" t="n">
-        <v>28.742</v>
+        <v>28.182</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.34</v>
       </c>
       <c r="I103" t="n">
-        <v>0.747</v>
+        <v>0.731</v>
       </c>
       <c r="J103" t="n">
-        <v>26.145</v>
+        <v>25.585</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.03</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1198</v>
+        <v>0.0977</v>
       </c>
       <c r="J104" t="n">
-        <v>4.193</v>
+        <v>3.4195</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.96</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.189</v>
+        <v>-0.1544</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.615</v>
+        <v>-5.404</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.83</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5392</v>
+        <v>-0.4991</v>
       </c>
       <c r="J106" t="n">
-        <v>-18.872</v>
+        <v>-17.4685</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.07</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1926</v>
+        <v>0.1524</v>
       </c>
       <c r="J107" t="n">
-        <v>6.741</v>
+        <v>5.334</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.02</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0741</v>
+        <v>0.0528</v>
       </c>
       <c r="J108" t="n">
-        <v>2.5935</v>
+        <v>1.848</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.02</v>
       </c>
       <c r="I109" t="n">
-        <v>0.0741</v>
+        <v>0.0528</v>
       </c>
       <c r="J109" t="n">
-        <v>2.5935</v>
+        <v>1.848</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.97</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.0578</v>
+        <v>-0.0454</v>
       </c>
       <c r="J110" t="n">
-        <v>-2.023</v>
+        <v>-1.589</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.89</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.1577</v>
+        <v>-0.1378</v>
       </c>
       <c r="J111" t="n">
-        <v>-5.5195</v>
+        <v>-4.823</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.59</v>
       </c>
       <c r="I112" t="n">
-        <v>1.07</v>
+        <v>1.0601</v>
       </c>
       <c r="J112" t="n">
-        <v>25.68</v>
+        <v>25.4424</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.34</v>
       </c>
       <c r="I113" t="n">
-        <v>0.7247</v>
+        <v>0.7111</v>
       </c>
       <c r="J113" t="n">
-        <v>17.3928</v>
+        <v>17.0664</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.25</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5915</v>
+        <v>0.5835</v>
       </c>
       <c r="J114" t="n">
-        <v>14.196</v>
+        <v>14.004</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.14</v>
       </c>
       <c r="I115" t="n">
-        <v>0.4039</v>
+        <v>0.3709</v>
       </c>
       <c r="J115" t="n">
-        <v>9.6936</v>
+        <v>8.9016</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.87</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4642</v>
+        <v>-0.4248</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.1408</v>
+        <v>-10.1952</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.35</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6268</v>
+        <v>0.5994</v>
       </c>
       <c r="J117" t="n">
-        <v>15.0432</v>
+        <v>14.3856</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.22</v>
       </c>
       <c r="I118" t="n">
-        <v>0.4706</v>
+        <v>0.4243</v>
       </c>
       <c r="J118" t="n">
-        <v>11.2944</v>
+        <v>10.1832</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0953</v>
+        <v>-0.0798</v>
       </c>
       <c r="J119" t="n">
-        <v>-2.2872</v>
+        <v>-1.9152</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.67</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3702</v>
+        <v>-0.3567</v>
       </c>
       <c r="J120" t="n">
-        <v>-8.8848</v>
+        <v>-8.5608</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.55</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4761</v>
+        <v>-0.4739</v>
       </c>
       <c r="J121" t="n">
-        <v>-11.4264</v>
+        <v>-11.3736</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.3</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6851</v>
+        <v>0.6701</v>
       </c>
       <c r="J122" t="n">
-        <v>19.8679</v>
+        <v>19.4329</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.18</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4933</v>
+        <v>0.4735</v>
       </c>
       <c r="J123" t="n">
-        <v>14.3057</v>
+        <v>13.7315</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.17</v>
       </c>
       <c r="I124" t="n">
-        <v>0.4764</v>
+        <v>0.4508</v>
       </c>
       <c r="J124" t="n">
-        <v>13.8156</v>
+        <v>13.0732</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.06</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2137</v>
+        <v>0.1833</v>
       </c>
       <c r="J125" t="n">
-        <v>6.1973</v>
+        <v>5.3157</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.87</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4424</v>
+        <v>-0.4001</v>
       </c>
       <c r="J126" t="n">
-        <v>-12.8296</v>
+        <v>-11.6029</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.51</v>
       </c>
       <c r="I127" t="n">
-        <v>0.769</v>
+        <v>0.7325</v>
       </c>
       <c r="J127" t="n">
-        <v>22.301</v>
+        <v>21.2425</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.38</v>
       </c>
       <c r="I128" t="n">
-        <v>0.6303</v>
+        <v>0.5997</v>
       </c>
       <c r="J128" t="n">
-        <v>18.2787</v>
+        <v>17.3913</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.16</v>
       </c>
       <c r="I129" t="n">
-        <v>0.3492</v>
+        <v>0.2968</v>
       </c>
       <c r="J129" t="n">
-        <v>10.1268</v>
+        <v>8.607200000000001</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2496</v>
+        <v>-0.23</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.2384</v>
+        <v>-6.67</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.55</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4864</v>
+        <v>-0.4873</v>
       </c>
       <c r="J131" t="n">
-        <v>-14.1056</v>
+        <v>-14.1317</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.54</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0139</v>
+        <v>1.0019</v>
       </c>
       <c r="J132" t="n">
-        <v>21.2919</v>
+        <v>21.0399</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.45</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8895999999999999</v>
+        <v>0.8744</v>
       </c>
       <c r="J133" t="n">
-        <v>18.6816</v>
+        <v>18.3624</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.07</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2303</v>
+        <v>0.2005</v>
       </c>
       <c r="J134" t="n">
-        <v>4.8363</v>
+        <v>4.2105</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.06</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2014</v>
+        <v>0.1731</v>
       </c>
       <c r="J135" t="n">
-        <v>4.2294</v>
+        <v>3.6351</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.83</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5536</v>
+        <v>-0.5159</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.6256</v>
+        <v>-10.8339</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.22</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4689</v>
+        <v>0.4218</v>
       </c>
       <c r="J137" t="n">
-        <v>9.8469</v>
+        <v>8.857799999999999</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.2</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4417</v>
+        <v>0.3882</v>
       </c>
       <c r="J138" t="n">
-        <v>9.275700000000001</v>
+        <v>8.152200000000001</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.08</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2211</v>
+        <v>0.1772</v>
       </c>
       <c r="J139" t="n">
-        <v>4.6431</v>
+        <v>3.7212</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.65</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3889</v>
+        <v>-0.3772</v>
       </c>
       <c r="J140" t="n">
-        <v>-8.1669</v>
+        <v>-7.9212</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.62</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4157</v>
+        <v>-0.4066</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.729699999999999</v>
+        <v>-8.538600000000001</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.96</v>
       </c>
       <c r="I142" t="n">
-        <v>1.498</v>
+        <v>1.5164</v>
       </c>
       <c r="J142" t="n">
-        <v>25.466</v>
+        <v>25.7788</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.49</v>
       </c>
       <c r="I143" t="n">
-        <v>0.9122</v>
+        <v>0.9009</v>
       </c>
       <c r="J143" t="n">
-        <v>15.5074</v>
+        <v>15.3153</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.31</v>
       </c>
       <c r="I144" t="n">
-        <v>0.6677</v>
+        <v>0.6611</v>
       </c>
       <c r="J144" t="n">
-        <v>11.3509</v>
+        <v>11.2387</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.26</v>
       </c>
       <c r="I145" t="n">
-        <v>0.5931</v>
+        <v>0.5891999999999999</v>
       </c>
       <c r="J145" t="n">
-        <v>10.0827</v>
+        <v>10.0164</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.93</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3276</v>
+        <v>-0.293</v>
       </c>
       <c r="J146" t="n">
-        <v>-5.5692</v>
+        <v>-4.981</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>0.93</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.0752</v>
+        <v>-0.0601</v>
       </c>
       <c r="J147" t="n">
-        <v>-1.2784</v>
+        <v>-1.0217</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.74</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.2826</v>
+        <v>-0.2683</v>
       </c>
       <c r="J148" t="n">
-        <v>-4.8042</v>
+        <v>-4.5611</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.327</v>
+        <v>-0.313</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.559</v>
+        <v>-5.321</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.63</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3804</v>
+        <v>-0.3682</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.4668</v>
+        <v>-6.2594</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4425</v>
+        <v>-0.4348</v>
       </c>
       <c r="J151" t="n">
-        <v>-7.5225</v>
+        <v>-7.3916</v>
       </c>
     </row>
   </sheetData>
